--- a/AHR 30th/output/AHR_data 30th.xlsx
+++ b/AHR 30th/output/AHR_data 30th.xlsx
@@ -6958,6 +6958,15 @@
       <c r="U52">
         <v>20476</v>
       </c>
+      <c r="V52">
+        <v>508600.1860000001</v>
+      </c>
+      <c r="W52">
+        <v>1289802.93042</v>
+      </c>
+      <c r="X52">
+        <v>1413184.333949999</v>
+      </c>
       <c r="Y52">
         <v>620505</v>
       </c>
@@ -6999,6 +7008,15 @@
       </c>
       <c r="AL52">
         <v>6.725167403969349</v>
+      </c>
+      <c r="AM52">
+        <v>1.151002331721522</v>
+      </c>
+      <c r="AN52">
+        <v>0.9604568037355969</v>
+      </c>
+      <c r="AO52">
+        <v>1.44892633664905</v>
       </c>
     </row>
   </sheetData>
@@ -7164,12 +7182,18 @@
           <t>Alabama</t>
         </is>
       </c>
+      <c r="B2">
+        <v>0.950295253754483</v>
+      </c>
       <c r="C2">
         <v>0.4982504445757104</v>
       </c>
       <c r="D2">
         <v>0.3473121067993641</v>
       </c>
+      <c r="E2">
+        <v>1.343662560004414</v>
+      </c>
       <c r="F2">
         <v>0.7162469410731637</v>
       </c>
@@ -7179,6 +7203,9 @@
       <c r="H2">
         <v>0.1399375400426623</v>
       </c>
+      <c r="I2">
+        <v>1.105390411122654</v>
+      </c>
       <c r="J2">
         <v>0.6689439992988344</v>
       </c>
@@ -7195,7 +7222,10 @@
         <v>0.2155470273512655</v>
       </c>
       <c r="O2">
-        <v>0.473126743259761</v>
+        <v>0.6254319736522431</v>
+      </c>
+      <c r="P2">
+        <v>29</v>
       </c>
       <c r="Q2">
         <v>9</v>
@@ -7203,6 +7233,9 @@
       <c r="R2">
         <v>11</v>
       </c>
+      <c r="S2">
+        <v>41</v>
+      </c>
       <c r="T2">
         <v>30</v>
       </c>
@@ -7212,6 +7245,9 @@
       <c r="V2">
         <v>3</v>
       </c>
+      <c r="W2">
+        <v>36</v>
+      </c>
       <c r="X2">
         <v>23</v>
       </c>
@@ -7237,12 +7273,18 @@
           <t>Alaska</t>
         </is>
       </c>
+      <c r="B3">
+        <v>0.6802945072684946</v>
+      </c>
       <c r="C3">
         <v>1.173677114643309</v>
       </c>
       <c r="D3">
         <v>13.39337924689598</v>
       </c>
+      <c r="E3">
+        <v>1.665147672023079</v>
+      </c>
       <c r="F3">
         <v>4.926132398160296</v>
       </c>
@@ -7252,6 +7294,9 @@
       <c r="H3">
         <v>0.4668749420907918</v>
       </c>
+      <c r="I3">
+        <v>1.313345288989801</v>
+      </c>
       <c r="J3">
         <v>0.3792932045112647</v>
       </c>
@@ -7268,7 +7313,10 @@
         <v>0.6516496839366721</v>
       </c>
       <c r="O3">
-        <v>2.482171286864272</v>
+        <v>2.190807718224931</v>
+      </c>
+      <c r="P3">
+        <v>7</v>
       </c>
       <c r="Q3">
         <v>36</v>
@@ -7276,6 +7324,9 @@
       <c r="R3">
         <v>50</v>
       </c>
+      <c r="S3">
+        <v>48</v>
+      </c>
       <c r="T3">
         <v>49</v>
       </c>
@@ -7285,6 +7336,9 @@
       <c r="V3">
         <v>15</v>
       </c>
+      <c r="W3">
+        <v>45</v>
+      </c>
       <c r="X3">
         <v>11</v>
       </c>
@@ -7310,12 +7364,18 @@
           <t>Arizona</t>
         </is>
       </c>
+      <c r="B4">
+        <v>1.466319932263327</v>
+      </c>
       <c r="C4">
         <v>0.1717114563025056</v>
       </c>
       <c r="D4">
         <v>2.321246711943953</v>
       </c>
+      <c r="E4">
+        <v>1.249315199954809</v>
+      </c>
       <c r="F4">
         <v>1.554527621050309</v>
       </c>
@@ -7325,6 +7385,9 @@
       <c r="H4">
         <v>0.6239471128146915</v>
       </c>
+      <c r="I4">
+        <v>1.286241530983455</v>
+      </c>
       <c r="J4">
         <v>0.601583770847452</v>
       </c>
@@ -7341,7 +7404,10 @@
         <v>1.700070249601834</v>
       </c>
       <c r="O4">
-        <v>1.186907712370642</v>
+        <v>1.220842598992924</v>
+      </c>
+      <c r="P4">
+        <v>49</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -7349,6 +7415,9 @@
       <c r="R4">
         <v>46</v>
       </c>
+      <c r="S4">
+        <v>39</v>
+      </c>
       <c r="T4">
         <v>42</v>
       </c>
@@ -7358,6 +7427,9 @@
       <c r="V4">
         <v>21</v>
       </c>
+      <c r="W4">
+        <v>43</v>
+      </c>
       <c r="X4">
         <v>22</v>
       </c>
@@ -7374,7 +7446,7 @@
         <v>43</v>
       </c>
       <c r="AC4">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -7383,12 +7455,18 @@
           <t>Arkansas</t>
         </is>
       </c>
+      <c r="B5">
+        <v>1.19394953576997</v>
+      </c>
       <c r="C5">
         <v>0.8068553187777977</v>
       </c>
       <c r="D5">
         <v>0.7434780105210955</v>
       </c>
+      <c r="E5">
+        <v>1.556687422880544</v>
+      </c>
       <c r="F5">
         <v>0.9010387909875616</v>
       </c>
@@ -7398,6 +7476,9 @@
       <c r="H5">
         <v>0.6642285959332423</v>
       </c>
+      <c r="I5">
+        <v>1.022647015207217</v>
+      </c>
       <c r="J5">
         <v>1.009822717626607</v>
       </c>
@@ -7414,7 +7495,10 @@
         <v>0.3167269599855835</v>
       </c>
       <c r="O5">
-        <v>0.6644939220863594</v>
+        <v>0.8014017842093326</v>
+      </c>
+      <c r="P5">
+        <v>42</v>
       </c>
       <c r="Q5">
         <v>22</v>
@@ -7422,6 +7506,9 @@
       <c r="R5">
         <v>22</v>
       </c>
+      <c r="S5">
+        <v>47</v>
+      </c>
       <c r="T5">
         <v>36</v>
       </c>
@@ -7431,6 +7518,9 @@
       <c r="V5">
         <v>24</v>
       </c>
+      <c r="W5">
+        <v>26</v>
+      </c>
       <c r="X5">
         <v>33</v>
       </c>
@@ -7447,7 +7537,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -7456,12 +7546,18 @@
           <t>California</t>
         </is>
       </c>
+      <c r="B6">
+        <v>1.143708785941803</v>
+      </c>
       <c r="C6">
         <v>0.8784337083399248</v>
       </c>
       <c r="D6">
         <v>1.858948492856903</v>
       </c>
+      <c r="E6">
+        <v>1.006465391999526</v>
+      </c>
       <c r="F6">
         <v>2.756007519587798</v>
       </c>
@@ -7471,6 +7567,9 @@
       <c r="H6">
         <v>2.426753188717774</v>
       </c>
+      <c r="I6">
+        <v>0.9500758615639947</v>
+      </c>
       <c r="J6">
         <v>1.823141479848573</v>
       </c>
@@ -7487,7 +7586,10 @@
         <v>1.478503991133346</v>
       </c>
       <c r="O6">
-        <v>1.65733689118274</v>
+        <v>1.513355303948671</v>
+      </c>
+      <c r="P6">
+        <v>39</v>
       </c>
       <c r="Q6">
         <v>24</v>
@@ -7495,6 +7597,9 @@
       <c r="R6">
         <v>41</v>
       </c>
+      <c r="S6">
+        <v>30</v>
+      </c>
       <c r="T6">
         <v>45</v>
       </c>
@@ -7504,6 +7609,9 @@
       <c r="V6">
         <v>50</v>
       </c>
+      <c r="W6">
+        <v>23</v>
+      </c>
       <c r="X6">
         <v>47</v>
       </c>
@@ -7520,7 +7628,7 @@
         <v>41</v>
       </c>
       <c r="AC6">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -7529,12 +7637,18 @@
           <t>Colorado</t>
         </is>
       </c>
+      <c r="B7">
+        <v>0.8916396646265115</v>
+      </c>
       <c r="C7">
         <v>0.7165233596745549</v>
       </c>
       <c r="D7">
         <v>1.750307216898924</v>
       </c>
+      <c r="E7">
+        <v>1.150265683737659</v>
+      </c>
       <c r="F7">
         <v>3.530626951776008</v>
       </c>
@@ -7544,6 +7658,9 @@
       <c r="H7">
         <v>0.9588068257021187</v>
       </c>
+      <c r="I7">
+        <v>1.240347254674201</v>
+      </c>
       <c r="J7">
         <v>1.562052877917234</v>
       </c>
@@ -7560,7 +7677,10 @@
         <v>0.9739404538803551</v>
       </c>
       <c r="O7">
-        <v>1.355715567150904</v>
+        <v>1.295339098042109</v>
+      </c>
+      <c r="P7">
+        <v>18</v>
       </c>
       <c r="Q7">
         <v>18</v>
@@ -7568,6 +7688,9 @@
       <c r="R7">
         <v>37</v>
       </c>
+      <c r="S7">
+        <v>35</v>
+      </c>
       <c r="T7">
         <v>48</v>
       </c>
@@ -7577,6 +7700,9 @@
       <c r="V7">
         <v>35</v>
       </c>
+      <c r="W7">
+        <v>41</v>
+      </c>
       <c r="X7">
         <v>45</v>
       </c>
@@ -7602,12 +7728,18 @@
           <t>Connecticut</t>
         </is>
       </c>
+      <c r="B8">
+        <v>1.002893870613157</v>
+      </c>
       <c r="C8">
         <v>0.7017458823413153</v>
       </c>
       <c r="D8">
         <v>1.797467721193777</v>
       </c>
+      <c r="E8">
+        <v>0.484274446768833</v>
+      </c>
       <c r="F8">
         <v>0.01538557866241582</v>
       </c>
@@ -7617,6 +7749,9 @@
       <c r="H8">
         <v>0.6526821733681566</v>
       </c>
+      <c r="I8">
+        <v>0.7493129479775652</v>
+      </c>
       <c r="J8">
         <v>0.3921757957905561</v>
       </c>
@@ -7633,7 +7768,10 @@
         <v>0.6957518110705576</v>
       </c>
       <c r="O8">
-        <v>0.6625899252624013</v>
+        <v>0.6817215783064283</v>
+      </c>
+      <c r="P8">
+        <v>32</v>
       </c>
       <c r="Q8">
         <v>16</v>
@@ -7641,6 +7779,9 @@
       <c r="R8">
         <v>40</v>
       </c>
+      <c r="S8">
+        <v>3</v>
+      </c>
       <c r="T8">
         <v>2</v>
       </c>
@@ -7650,6 +7791,9 @@
       <c r="V8">
         <v>23</v>
       </c>
+      <c r="W8">
+        <v>19</v>
+      </c>
       <c r="X8">
         <v>12</v>
       </c>
@@ -7666,7 +7810,7 @@
         <v>25</v>
       </c>
       <c r="AC8">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -7675,18 +7819,27 @@
           <t>Delaware</t>
         </is>
       </c>
+      <c r="B9">
+        <v>1.117822782681775</v>
+      </c>
       <c r="C9">
         <v>0.1875741991439067</v>
       </c>
       <c r="D9">
         <v>0.2756647948628159</v>
       </c>
+      <c r="E9">
+        <v>0.8197293018064832</v>
+      </c>
       <c r="G9">
         <v>1.691024825583768</v>
       </c>
       <c r="H9">
         <v>0.4122126920757007</v>
       </c>
+      <c r="I9">
+        <v>1.032132977934284</v>
+      </c>
       <c r="J9">
         <v>1.323094096015478</v>
       </c>
@@ -7703,7 +7856,10 @@
         <v>0.8753044311214823</v>
       </c>
       <c r="O9">
-        <v>0.9647612009956837</v>
+        <v>0.9710446559486414</v>
+      </c>
+      <c r="P9">
+        <v>37</v>
       </c>
       <c r="Q9">
         <v>4</v>
@@ -7711,12 +7867,18 @@
       <c r="R9">
         <v>8</v>
       </c>
+      <c r="S9">
+        <v>18</v>
+      </c>
       <c r="U9">
         <v>49</v>
       </c>
       <c r="V9">
         <v>13</v>
       </c>
+      <c r="W9">
+        <v>27</v>
+      </c>
       <c r="X9">
         <v>40</v>
       </c>
@@ -7733,7 +7895,7 @@
         <v>30</v>
       </c>
       <c r="AC9">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -7742,12 +7904,18 @@
           <t>Florida</t>
         </is>
       </c>
+      <c r="B10">
+        <v>0.8229960999016175</v>
+      </c>
       <c r="C10">
         <v>0.4151967377184102</v>
       </c>
       <c r="D10">
         <v>0.2284037734916452</v>
       </c>
+      <c r="E10">
+        <v>1.342469430930725</v>
+      </c>
       <c r="F10">
         <v>0.1346739857851094</v>
       </c>
@@ -7757,6 +7925,9 @@
       <c r="H10">
         <v>0.1880272757140078</v>
       </c>
+      <c r="I10">
+        <v>1.223968922866506</v>
+      </c>
       <c r="J10">
         <v>0.2407397819349428</v>
       </c>
@@ -7773,7 +7944,10 @@
         <v>0.4229156193981897</v>
       </c>
       <c r="O10">
-        <v>0.5591142014605908</v>
+        <v>0.6908135744849813</v>
+      </c>
+      <c r="P10">
+        <v>14</v>
       </c>
       <c r="Q10">
         <v>6</v>
@@ -7781,6 +7955,9 @@
       <c r="R10">
         <v>6</v>
       </c>
+      <c r="S10">
+        <v>40</v>
+      </c>
       <c r="T10">
         <v>5</v>
       </c>
@@ -7790,6 +7967,9 @@
       <c r="V10">
         <v>4</v>
       </c>
+      <c r="W10">
+        <v>39</v>
+      </c>
       <c r="X10">
         <v>6</v>
       </c>
@@ -7806,7 +7986,7 @@
         <v>13</v>
       </c>
       <c r="AC10">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -7815,12 +7995,18 @@
           <t>Georgia</t>
         </is>
       </c>
+      <c r="B11">
+        <v>0.9188428944802592</v>
+      </c>
       <c r="C11">
         <v>0.2368229079376493</v>
       </c>
       <c r="D11">
         <v>0.1609624012231248</v>
       </c>
+      <c r="E11">
+        <v>0.7216986874631109</v>
+      </c>
       <c r="F11">
         <v>0.4155847227491939</v>
       </c>
@@ -7830,6 +8016,9 @@
       <c r="H11">
         <v>0.1345364403216295</v>
       </c>
+      <c r="I11">
+        <v>1.073611067757111</v>
+      </c>
       <c r="J11">
         <v>0.3453856511779232</v>
       </c>
@@ -7846,7 +8035,10 @@
         <v>0.3780956870288102</v>
       </c>
       <c r="O11">
-        <v>0.5470423603079974</v>
+        <v>0.6295827886754196</v>
+      </c>
+      <c r="P11">
+        <v>24</v>
       </c>
       <c r="Q11">
         <v>5</v>
@@ -7854,6 +8046,9 @@
       <c r="R11">
         <v>3</v>
       </c>
+      <c r="S11">
+        <v>13</v>
+      </c>
       <c r="T11">
         <v>15</v>
       </c>
@@ -7863,6 +8058,9 @@
       <c r="V11">
         <v>2</v>
       </c>
+      <c r="W11">
+        <v>32</v>
+      </c>
       <c r="X11">
         <v>8</v>
       </c>
@@ -7879,7 +8077,7 @@
         <v>8</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -7888,12 +8086,18 @@
           <t>Hawaii</t>
         </is>
       </c>
+      <c r="B12">
+        <v>0.4683796472996711</v>
+      </c>
       <c r="C12">
         <v>0.9705627028506626</v>
       </c>
       <c r="D12">
         <v>3.95296086147177</v>
       </c>
+      <c r="E12">
+        <v>2.730846823079459</v>
+      </c>
       <c r="F12">
         <v>3.433092135917911</v>
       </c>
@@ -7903,6 +8107,9 @@
       <c r="H12">
         <v>1.024243729869131</v>
       </c>
+      <c r="I12">
+        <v>1.190882996942366</v>
+      </c>
       <c r="J12">
         <v>3.786928095577968</v>
       </c>
@@ -7919,7 +8126,10 @@
         <v>0.3065714900436239</v>
       </c>
       <c r="O12">
-        <v>1.570203652066729</v>
+        <v>1.545549691383753</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
       </c>
       <c r="Q12">
         <v>30</v>
@@ -7927,6 +8137,9 @@
       <c r="R12">
         <v>48</v>
       </c>
+      <c r="S12">
+        <v>49</v>
+      </c>
       <c r="T12">
         <v>47</v>
       </c>
@@ -7936,6 +8149,9 @@
       <c r="V12">
         <v>38</v>
       </c>
+      <c r="W12">
+        <v>38</v>
+      </c>
       <c r="X12">
         <v>50</v>
       </c>
@@ -7952,7 +8168,7 @@
         <v>5</v>
       </c>
       <c r="AC12">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -7961,12 +8177,18 @@
           <t>Idaho</t>
         </is>
       </c>
+      <c r="B13">
+        <v>0.8924530095274993</v>
+      </c>
       <c r="C13">
         <v>0.7280136791729949</v>
       </c>
       <c r="D13">
         <v>0.8587414215994613</v>
       </c>
+      <c r="E13">
+        <v>1.237232206996926</v>
+      </c>
       <c r="F13">
         <v>0.4811921118629402</v>
       </c>
@@ -7976,6 +8198,9 @@
       <c r="H13">
         <v>0.9454795402431234</v>
       </c>
+      <c r="I13">
+        <v>0.6973193688230925</v>
+      </c>
       <c r="J13">
         <v>0.4020466045449957</v>
       </c>
@@ -7992,7 +8217,10 @@
         <v>1.067121333690954</v>
       </c>
       <c r="O13">
-        <v>0.8467107385875292</v>
+        <v>0.8687778439402162</v>
+      </c>
+      <c r="P13">
+        <v>19</v>
       </c>
       <c r="Q13">
         <v>19</v>
@@ -8000,6 +8228,9 @@
       <c r="R13">
         <v>26</v>
       </c>
+      <c r="S13">
+        <v>38</v>
+      </c>
       <c r="T13">
         <v>18</v>
       </c>
@@ -8009,6 +8240,9 @@
       <c r="V13">
         <v>34</v>
       </c>
+      <c r="W13">
+        <v>11</v>
+      </c>
       <c r="X13">
         <v>15</v>
       </c>
@@ -8025,7 +8259,7 @@
         <v>35</v>
       </c>
       <c r="AC13">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -8034,12 +8268,18 @@
           <t>Illinois</t>
         </is>
       </c>
+      <c r="B14">
+        <v>0.9124938913242251</v>
+      </c>
       <c r="C14">
         <v>1.389875877970298</v>
       </c>
       <c r="D14">
         <v>2.271721609045647</v>
       </c>
+      <c r="E14">
+        <v>0.8308448204918795</v>
+      </c>
       <c r="F14">
         <v>0.6529803823467585</v>
       </c>
@@ -8049,6 +8289,9 @@
       <c r="H14">
         <v>0.8781608144151217</v>
       </c>
+      <c r="I14">
+        <v>1.011326084198319</v>
+      </c>
       <c r="J14">
         <v>1.055859294650753</v>
       </c>
@@ -8065,7 +8308,10 @@
         <v>0.9693590631197845</v>
       </c>
       <c r="O14">
-        <v>1.114509803423374</v>
+        <v>1.069212525403705</v>
+      </c>
+      <c r="P14">
+        <v>22</v>
       </c>
       <c r="Q14">
         <v>40</v>
@@ -8073,6 +8319,9 @@
       <c r="R14">
         <v>45</v>
       </c>
+      <c r="S14">
+        <v>20</v>
+      </c>
       <c r="T14">
         <v>27</v>
       </c>
@@ -8082,6 +8331,9 @@
       <c r="V14">
         <v>33</v>
       </c>
+      <c r="W14">
+        <v>25</v>
+      </c>
       <c r="X14">
         <v>36</v>
       </c>
@@ -8107,12 +8359,18 @@
           <t>Indiana</t>
         </is>
       </c>
+      <c r="B15">
+        <v>0.7099152952082147</v>
+      </c>
       <c r="C15">
         <v>0.7764642042633283</v>
       </c>
       <c r="D15">
         <v>0.3197317837348382</v>
       </c>
+      <c r="E15">
+        <v>0.9053842169575864</v>
+      </c>
       <c r="F15">
         <v>1.419707906733865</v>
       </c>
@@ -8122,6 +8380,9 @@
       <c r="H15">
         <v>0.2176702867692597</v>
       </c>
+      <c r="I15">
+        <v>0.7165089607640709</v>
+      </c>
       <c r="J15">
         <v>1.017754487455121</v>
       </c>
@@ -8138,7 +8399,10 @@
         <v>0.2026709050837961</v>
       </c>
       <c r="O15">
-        <v>0.9187029703155221</v>
+        <v>0.8860644750834686</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
       </c>
       <c r="Q15">
         <v>20</v>
@@ -8146,6 +8410,9 @@
       <c r="R15">
         <v>10</v>
       </c>
+      <c r="S15">
+        <v>25</v>
+      </c>
       <c r="T15">
         <v>41</v>
       </c>
@@ -8155,6 +8422,9 @@
       <c r="V15">
         <v>7</v>
       </c>
+      <c r="W15">
+        <v>16</v>
+      </c>
       <c r="X15">
         <v>35</v>
       </c>
@@ -8171,7 +8441,7 @@
         <v>3</v>
       </c>
       <c r="AC15">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -8180,12 +8450,18 @@
           <t>Iowa</t>
         </is>
       </c>
+      <c r="B16">
+        <v>1.09286770924452</v>
+      </c>
       <c r="C16">
         <v>2.84864839585236</v>
       </c>
       <c r="D16">
         <v>1.601204011308867</v>
       </c>
+      <c r="E16">
+        <v>0.5572152520651036</v>
+      </c>
       <c r="F16">
         <v>0.8709895404728789</v>
       </c>
@@ -8195,6 +8471,9 @@
       <c r="H16">
         <v>0.6791801153171246</v>
       </c>
+      <c r="I16">
+        <v>0.6744555320784841</v>
+      </c>
       <c r="J16">
         <v>0.7578249422861457</v>
       </c>
@@ -8211,7 +8490,10 @@
         <v>0.5774957165281422</v>
       </c>
       <c r="O16">
-        <v>1.06223463584407</v>
+        <v>0.9959142193714471</v>
+      </c>
+      <c r="P16">
+        <v>34</v>
       </c>
       <c r="Q16">
         <v>50</v>
@@ -8219,6 +8501,9 @@
       <c r="R16">
         <v>36</v>
       </c>
+      <c r="S16">
+        <v>8</v>
+      </c>
       <c r="T16">
         <v>35</v>
       </c>
@@ -8228,6 +8513,9 @@
       <c r="V16">
         <v>25</v>
       </c>
+      <c r="W16">
+        <v>10</v>
+      </c>
       <c r="X16">
         <v>27</v>
       </c>
@@ -8244,7 +8532,7 @@
         <v>18</v>
       </c>
       <c r="AC16">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -8253,12 +8541,18 @@
           <t>Kansas</t>
         </is>
       </c>
+      <c r="B17">
+        <v>0.9107626567351403</v>
+      </c>
       <c r="C17">
         <v>0.7824804778298806</v>
       </c>
       <c r="D17">
         <v>0.3560492868934582</v>
       </c>
+      <c r="E17">
+        <v>0.809357599602629</v>
+      </c>
       <c r="F17">
         <v>0.2422079025203656</v>
       </c>
@@ -8268,6 +8562,9 @@
       <c r="H17">
         <v>0.5219836391279373</v>
       </c>
+      <c r="I17">
+        <v>0.6991019231996349</v>
+      </c>
       <c r="J17">
         <v>0.580117266099155</v>
       </c>
@@ -8284,7 +8581,10 @@
         <v>3.679793821809112</v>
       </c>
       <c r="O17">
-        <v>0.9791584141630237</v>
+        <v>0.9392927939359724</v>
+      </c>
+      <c r="P17">
+        <v>21</v>
       </c>
       <c r="Q17">
         <v>21</v>
@@ -8292,6 +8592,9 @@
       <c r="R17">
         <v>12</v>
       </c>
+      <c r="S17">
+        <v>17</v>
+      </c>
       <c r="T17">
         <v>11</v>
       </c>
@@ -8301,6 +8604,9 @@
       <c r="V17">
         <v>17</v>
       </c>
+      <c r="W17">
+        <v>13</v>
+      </c>
       <c r="X17">
         <v>20</v>
       </c>
@@ -8317,7 +8623,7 @@
         <v>49</v>
       </c>
       <c r="AC17">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -8326,12 +8632,18 @@
           <t>Kentucky</t>
         </is>
       </c>
+      <c r="B18">
+        <v>1.340443518757872</v>
+      </c>
       <c r="C18">
         <v>1.095691755021232</v>
       </c>
       <c r="D18">
         <v>0.2129813341281091</v>
       </c>
+      <c r="E18">
+        <v>0.8893343460441584</v>
+      </c>
       <c r="F18">
         <v>0.4143413379172157</v>
       </c>
@@ -8341,6 +8653,9 @@
       <c r="H18">
         <v>0.2430269471965881</v>
       </c>
+      <c r="I18">
+        <v>1.006227683956952</v>
+      </c>
       <c r="J18">
         <v>1.01765876910368</v>
       </c>
@@ -8357,7 +8672,10 @@
         <v>0.6780783992328946</v>
       </c>
       <c r="O18">
-        <v>0.5792321120344598</v>
+        <v>0.6944866668541215</v>
+      </c>
+      <c r="P18">
+        <v>46</v>
       </c>
       <c r="Q18">
         <v>33</v>
@@ -8365,6 +8683,9 @@
       <c r="R18">
         <v>5</v>
       </c>
+      <c r="S18">
+        <v>23</v>
+      </c>
       <c r="T18">
         <v>14</v>
       </c>
@@ -8374,6 +8695,9 @@
       <c r="V18">
         <v>8</v>
       </c>
+      <c r="W18">
+        <v>24</v>
+      </c>
       <c r="X18">
         <v>34</v>
       </c>
@@ -8390,7 +8714,7 @@
         <v>24</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -8399,12 +8723,18 @@
           <t>Louisiana</t>
         </is>
       </c>
+      <c r="B19">
+        <v>1.113452289729006</v>
+      </c>
       <c r="C19">
         <v>1.707336409533238</v>
       </c>
       <c r="D19">
         <v>2.986195599792868</v>
       </c>
+      <c r="E19">
+        <v>0.8420013247354865</v>
+      </c>
       <c r="F19">
         <v>1.795872724591548</v>
       </c>
@@ -8414,6 +8744,9 @@
       <c r="H19">
         <v>1.267565002683829</v>
       </c>
+      <c r="I19">
+        <v>1.2489285771852</v>
+      </c>
       <c r="J19">
         <v>2.726482932022324</v>
       </c>
@@ -8430,7 +8763,10 @@
         <v>0.3829849766430218</v>
       </c>
       <c r="O19">
-        <v>1.342800154952021</v>
+        <v>1.279414133936146</v>
+      </c>
+      <c r="P19">
+        <v>36</v>
       </c>
       <c r="Q19">
         <v>44</v>
@@ -8438,6 +8774,9 @@
       <c r="R19">
         <v>47</v>
       </c>
+      <c r="S19">
+        <v>22</v>
+      </c>
       <c r="T19">
         <v>43</v>
       </c>
@@ -8447,6 +8786,9 @@
       <c r="V19">
         <v>42</v>
       </c>
+      <c r="W19">
+        <v>42</v>
+      </c>
       <c r="X19">
         <v>49</v>
       </c>
@@ -8472,12 +8814,18 @@
           <t>Maine</t>
         </is>
       </c>
+      <c r="B20">
+        <v>0.9484639694737076</v>
+      </c>
       <c r="C20">
         <v>2.291252229097871</v>
       </c>
       <c r="D20">
         <v>1.885779083025577</v>
       </c>
+      <c r="E20">
+        <v>0.9363392785887356</v>
+      </c>
       <c r="F20">
         <v>0.0885183705700481</v>
       </c>
@@ -8487,6 +8835,9 @@
       <c r="H20">
         <v>0.7543100415613085</v>
       </c>
+      <c r="I20">
+        <v>0.5235715873475935</v>
+      </c>
       <c r="J20">
         <v>0.09959238850761926</v>
       </c>
@@ -8503,7 +8854,10 @@
         <v>0.6198820721727675</v>
       </c>
       <c r="O20">
-        <v>0.858408900502364</v>
+        <v>0.8455741415718212</v>
+      </c>
+      <c r="P20">
+        <v>28</v>
       </c>
       <c r="Q20">
         <v>47</v>
@@ -8511,6 +8865,9 @@
       <c r="R20">
         <v>42</v>
       </c>
+      <c r="S20">
+        <v>28</v>
+      </c>
       <c r="T20">
         <v>4</v>
       </c>
@@ -8520,6 +8877,9 @@
       <c r="V20">
         <v>28</v>
       </c>
+      <c r="W20">
+        <v>3</v>
+      </c>
       <c r="X20">
         <v>3</v>
       </c>
@@ -8536,7 +8896,7 @@
         <v>22</v>
       </c>
       <c r="AC20">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -8545,12 +8905,18 @@
           <t>Maryland</t>
         </is>
       </c>
+      <c r="B21">
+        <v>0.7705075259201506</v>
+      </c>
       <c r="C21">
         <v>0.6778591508084953</v>
       </c>
       <c r="D21">
         <v>0.9297187348564605</v>
       </c>
+      <c r="E21">
+        <v>0.5194333980208908</v>
+      </c>
       <c r="F21">
         <v>0.6695223755510638</v>
       </c>
@@ -8560,6 +8926,9 @@
       <c r="H21">
         <v>1.401001582625498</v>
       </c>
+      <c r="I21">
+        <v>1.052742060076994</v>
+      </c>
       <c r="J21">
         <v>1.514256209933429</v>
       </c>
@@ -8576,7 +8945,10 @@
         <v>1.538742023810754</v>
       </c>
       <c r="O21">
-        <v>1.134990196922362</v>
+        <v>1.053275765633974</v>
+      </c>
+      <c r="P21">
+        <v>12</v>
       </c>
       <c r="Q21">
         <v>14</v>
@@ -8584,6 +8956,9 @@
       <c r="R21">
         <v>28</v>
       </c>
+      <c r="S21">
+        <v>7</v>
+      </c>
       <c r="T21">
         <v>28</v>
       </c>
@@ -8593,6 +8968,9 @@
       <c r="V21">
         <v>43</v>
       </c>
+      <c r="W21">
+        <v>28</v>
+      </c>
       <c r="X21">
         <v>44</v>
       </c>
@@ -8609,7 +8987,7 @@
         <v>42</v>
       </c>
       <c r="AC21">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22">
@@ -8618,12 +8996,18 @@
           <t>Massachusetts</t>
         </is>
       </c>
+      <c r="B22">
+        <v>0.4547831906943969</v>
+      </c>
       <c r="C22">
         <v>1.319613598206858</v>
       </c>
       <c r="D22">
         <v>0.1857955021365204</v>
       </c>
+      <c r="E22">
+        <v>0.6450663277860074</v>
+      </c>
       <c r="F22">
         <v>0.724303678241536</v>
       </c>
@@ -8633,6 +9017,9 @@
       <c r="H22">
         <v>1.550210486857843</v>
       </c>
+      <c r="I22">
+        <v>0.5448775822963089</v>
+      </c>
       <c r="J22">
         <v>0.6728119505155246</v>
       </c>
@@ -8649,7 +9036,10 @@
         <v>0.5929257361091261</v>
       </c>
       <c r="O22">
-        <v>0.9877358341168692</v>
+        <v>0.8863142647650311</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
       </c>
       <c r="Q22">
         <v>38</v>
@@ -8657,6 +9047,9 @@
       <c r="R22">
         <v>4</v>
       </c>
+      <c r="S22">
+        <v>11</v>
+      </c>
       <c r="T22">
         <v>31</v>
       </c>
@@ -8666,6 +9059,9 @@
       <c r="V22">
         <v>46</v>
       </c>
+      <c r="W22">
+        <v>6</v>
+      </c>
       <c r="X22">
         <v>24</v>
       </c>
@@ -8682,7 +9078,7 @@
         <v>21</v>
       </c>
       <c r="AC22">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -8691,12 +9087,18 @@
           <t>Michigan</t>
         </is>
       </c>
+      <c r="B23">
+        <v>0.944019525339535</v>
+      </c>
       <c r="C23">
         <v>1.675125581168334</v>
       </c>
       <c r="D23">
         <v>0.524930647902506</v>
       </c>
+      <c r="E23">
+        <v>0.7059485463342907</v>
+      </c>
       <c r="F23">
         <v>1.019248878529075</v>
       </c>
@@ -8706,6 +9108,9 @@
       <c r="H23">
         <v>0.8661395356055072</v>
       </c>
+      <c r="I23">
+        <v>0.8809362528146218</v>
+      </c>
       <c r="J23">
         <v>1.332849633143921</v>
       </c>
@@ -8722,7 +9127,10 @@
         <v>0.5471764420604555</v>
       </c>
       <c r="O23">
-        <v>0.8498971888632929</v>
+        <v>0.8484520163939521</v>
+      </c>
+      <c r="P23">
+        <v>27</v>
       </c>
       <c r="Q23">
         <v>43</v>
@@ -8730,6 +9138,9 @@
       <c r="R23">
         <v>19</v>
       </c>
+      <c r="S23">
+        <v>12</v>
+      </c>
       <c r="T23">
         <v>40</v>
       </c>
@@ -8739,6 +9150,9 @@
       <c r="V23">
         <v>32</v>
       </c>
+      <c r="W23">
+        <v>21</v>
+      </c>
       <c r="X23">
         <v>42</v>
       </c>
@@ -8755,7 +9169,7 @@
         <v>17</v>
       </c>
       <c r="AC23">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -8764,12 +9178,18 @@
           <t>Minnesota</t>
         </is>
       </c>
+      <c r="B24">
+        <v>0.6728656307420843</v>
+      </c>
       <c r="C24">
         <v>0.6604035262794286</v>
       </c>
       <c r="D24">
         <v>0.7453603100308376</v>
       </c>
+      <c r="E24">
+        <v>0.7800221010168312</v>
+      </c>
       <c r="F24">
         <v>0.1984027485362007</v>
       </c>
@@ -8779,6 +9199,9 @@
       <c r="H24">
         <v>0.1292740488965809</v>
       </c>
+      <c r="I24">
+        <v>0.3651674964875611</v>
+      </c>
       <c r="J24">
         <v>0.397867068708741</v>
       </c>
@@ -8795,7 +9218,10 @@
         <v>1.855265144785831</v>
       </c>
       <c r="O24">
-        <v>0.8065217238606521</v>
+        <v>0.7602517282194614</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>12</v>
@@ -8803,6 +9229,9 @@
       <c r="R24">
         <v>23</v>
       </c>
+      <c r="S24">
+        <v>15</v>
+      </c>
       <c r="T24">
         <v>8</v>
       </c>
@@ -8812,6 +9241,9 @@
       <c r="V24">
         <v>1</v>
       </c>
+      <c r="W24">
+        <v>2</v>
+      </c>
       <c r="X24">
         <v>13</v>
       </c>
@@ -8828,7 +9260,7 @@
         <v>45</v>
       </c>
       <c r="AC24">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -8837,12 +9269,18 @@
           <t>Mississippi</t>
         </is>
       </c>
+      <c r="B25">
+        <v>1.301650769842206</v>
+      </c>
       <c r="C25">
         <v>0.8963106515995202</v>
       </c>
       <c r="D25">
         <v>1.144299184004947</v>
       </c>
+      <c r="E25">
+        <v>1.436080898992177</v>
+      </c>
       <c r="F25">
         <v>0.9433471087059745</v>
       </c>
@@ -8852,6 +9290,9 @@
       <c r="H25">
         <v>0.8093364061548578</v>
       </c>
+      <c r="I25">
+        <v>1.562608501833805</v>
+      </c>
       <c r="J25">
         <v>1.123122797948854</v>
       </c>
@@ -8868,7 +9309,10 @@
         <v>0.3967361961034241</v>
       </c>
       <c r="O25">
-        <v>0.7088355867760722</v>
+        <v>0.8760535414176084</v>
+      </c>
+      <c r="P25">
+        <v>43</v>
       </c>
       <c r="Q25">
         <v>26</v>
@@ -8876,6 +9320,9 @@
       <c r="R25">
         <v>31</v>
       </c>
+      <c r="S25">
+        <v>43</v>
+      </c>
       <c r="T25">
         <v>38</v>
       </c>
@@ -8885,6 +9332,9 @@
       <c r="V25">
         <v>30</v>
       </c>
+      <c r="W25">
+        <v>49</v>
+      </c>
       <c r="X25">
         <v>38</v>
       </c>
@@ -8901,7 +9351,7 @@
         <v>10</v>
       </c>
       <c r="AC25">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -8910,12 +9360,18 @@
           <t>Missouri</t>
         </is>
       </c>
+      <c r="B26">
+        <v>0.7012911626834096</v>
+      </c>
       <c r="C26">
         <v>1.330634043614174</v>
       </c>
       <c r="D26">
         <v>0.4036881503501098</v>
       </c>
+      <c r="E26">
+        <v>0.9022837077654113</v>
+      </c>
       <c r="F26">
         <v>0.7270680665378959</v>
       </c>
@@ -8925,6 +9381,9 @@
       <c r="H26">
         <v>0.6274953054470301</v>
       </c>
+      <c r="I26">
+        <v>1.065825581467118</v>
+      </c>
       <c r="J26">
         <v>0.7777690204395585</v>
       </c>
@@ -8941,7 +9400,10 @@
         <v>0.8838371688299902</v>
       </c>
       <c r="O26">
-        <v>0.6697105386692026</v>
+        <v>0.7205004491236896</v>
+      </c>
+      <c r="P26">
+        <v>9</v>
       </c>
       <c r="Q26">
         <v>39</v>
@@ -8949,6 +9411,9 @@
       <c r="R26">
         <v>14</v>
       </c>
+      <c r="S26">
+        <v>24</v>
+      </c>
       <c r="T26">
         <v>32</v>
       </c>
@@ -8958,6 +9423,9 @@
       <c r="V26">
         <v>22</v>
       </c>
+      <c r="W26">
+        <v>31</v>
+      </c>
       <c r="X26">
         <v>28</v>
       </c>
@@ -8983,12 +9451,18 @@
           <t>Montana</t>
         </is>
       </c>
+      <c r="B27">
+        <v>1.163514246288838</v>
+      </c>
       <c r="C27">
         <v>1.013313270719777</v>
       </c>
       <c r="D27">
         <v>0.9620079293530099</v>
       </c>
+      <c r="E27">
+        <v>1.099186758154736</v>
+      </c>
       <c r="F27">
         <v>0.4682188669586645</v>
       </c>
@@ -8998,6 +9472,9 @@
       <c r="H27">
         <v>0.8238100361789056</v>
       </c>
+      <c r="I27">
+        <v>1.505984350641695</v>
+      </c>
       <c r="J27">
         <v>0.3994760157196676</v>
       </c>
@@ -9014,7 +9491,10 @@
         <v>0.7603879886187158</v>
       </c>
       <c r="O27">
-        <v>0.7745743753271712</v>
+        <v>0.8857253160274602</v>
+      </c>
+      <c r="P27">
+        <v>40</v>
       </c>
       <c r="Q27">
         <v>32</v>
@@ -9022,6 +9502,9 @@
       <c r="R27">
         <v>29</v>
       </c>
+      <c r="S27">
+        <v>34</v>
+      </c>
       <c r="T27">
         <v>17</v>
       </c>
@@ -9031,6 +9514,9 @@
       <c r="V27">
         <v>31</v>
       </c>
+      <c r="W27">
+        <v>48</v>
+      </c>
       <c r="X27">
         <v>14</v>
       </c>
@@ -9047,7 +9533,7 @@
         <v>28</v>
       </c>
       <c r="AC27">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -9056,12 +9542,18 @@
           <t>Nebraska</t>
         </is>
       </c>
+      <c r="B28">
+        <v>0.9153726677709252</v>
+      </c>
       <c r="C28">
         <v>1.175230796870274</v>
       </c>
       <c r="D28">
         <v>0.7593405197421154</v>
       </c>
+      <c r="E28">
+        <v>1.00636758042094</v>
+      </c>
       <c r="F28">
         <v>0.5277727777711805</v>
       </c>
@@ -9071,6 +9563,9 @@
       <c r="H28">
         <v>2.006390010233103</v>
       </c>
+      <c r="I28">
+        <v>0.8183571247844159</v>
+      </c>
       <c r="J28">
         <v>0.2758963970711671</v>
       </c>
@@ -9087,7 +9582,10 @@
         <v>0.5902752638181615</v>
       </c>
       <c r="O28">
-        <v>0.859283130622752</v>
+        <v>0.8717637445541385</v>
+      </c>
+      <c r="P28">
+        <v>23</v>
       </c>
       <c r="Q28">
         <v>37</v>
@@ -9095,6 +9593,9 @@
       <c r="R28">
         <v>25</v>
       </c>
+      <c r="S28">
+        <v>29</v>
+      </c>
       <c r="T28">
         <v>23</v>
       </c>
@@ -9104,6 +9605,9 @@
       <c r="V28">
         <v>49</v>
       </c>
+      <c r="W28">
+        <v>20</v>
+      </c>
       <c r="X28">
         <v>7</v>
       </c>
@@ -9120,7 +9624,7 @@
         <v>20</v>
       </c>
       <c r="AC28">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -9129,12 +9633,18 @@
           <t>Nevada</t>
         </is>
       </c>
+      <c r="B29">
+        <v>1.00310562737891</v>
+      </c>
       <c r="C29">
         <v>0.1700183134689107</v>
       </c>
       <c r="D29">
         <v>0.1528485071031518</v>
       </c>
+      <c r="E29">
+        <v>1.156512993917818</v>
+      </c>
       <c r="F29">
         <v>0.1394497076498046</v>
       </c>
@@ -9144,6 +9654,9 @@
       <c r="H29">
         <v>0.3610855846320352</v>
       </c>
+      <c r="I29">
+        <v>1.231339933039217</v>
+      </c>
       <c r="J29">
         <v>0.3617000084286194</v>
       </c>
@@ -9160,7 +9673,10 @@
         <v>1.133233195507545</v>
       </c>
       <c r="O29">
-        <v>0.8337691175769002</v>
+        <v>0.9022038253926883</v>
+      </c>
+      <c r="P29">
+        <v>33</v>
       </c>
       <c r="Q29">
         <v>1</v>
@@ -9168,6 +9684,9 @@
       <c r="R29">
         <v>2</v>
       </c>
+      <c r="S29">
+        <v>36</v>
+      </c>
       <c r="T29">
         <v>6</v>
       </c>
@@ -9177,6 +9696,9 @@
       <c r="V29">
         <v>11</v>
       </c>
+      <c r="W29">
+        <v>40</v>
+      </c>
       <c r="X29">
         <v>9</v>
       </c>
@@ -9193,7 +9715,7 @@
         <v>36</v>
       </c>
       <c r="AC29">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -9202,12 +9724,18 @@
           <t>New Hampshire</t>
         </is>
       </c>
+      <c r="B30">
+        <v>0.8262989289772738</v>
+      </c>
       <c r="C30">
         <v>1.117261212209998</v>
       </c>
       <c r="D30">
         <v>0.2780565329131561</v>
       </c>
+      <c r="E30">
+        <v>0.7810396514221293</v>
+      </c>
       <c r="F30">
         <v>0.07054786564547889</v>
       </c>
@@ -9217,6 +9745,9 @@
       <c r="H30">
         <v>0.3493831510969829</v>
       </c>
+      <c r="I30">
+        <v>0.7076147166818574</v>
+      </c>
       <c r="J30">
         <v>0</v>
       </c>
@@ -9233,7 +9764,10 @@
         <v>0.5881648038534175</v>
       </c>
       <c r="O30">
-        <v>0.6744714219098196</v>
+        <v>0.6968975012445736</v>
+      </c>
+      <c r="P30">
+        <v>16</v>
       </c>
       <c r="Q30">
         <v>34</v>
@@ -9241,6 +9775,9 @@
       <c r="R30">
         <v>9</v>
       </c>
+      <c r="S30">
+        <v>16</v>
+      </c>
       <c r="T30">
         <v>3</v>
       </c>
@@ -9250,6 +9787,9 @@
       <c r="V30">
         <v>10</v>
       </c>
+      <c r="W30">
+        <v>14</v>
+      </c>
       <c r="X30">
         <v>1</v>
       </c>
@@ -9266,7 +9806,7 @@
         <v>19</v>
       </c>
       <c r="AC30">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -9275,12 +9815,18 @@
           <t>New Jersey</t>
         </is>
       </c>
+      <c r="B31">
+        <v>0.6548248711751378</v>
+      </c>
       <c r="C31">
         <v>0.8929987573129358</v>
       </c>
       <c r="D31">
         <v>1.475209164352687</v>
       </c>
+      <c r="E31">
+        <v>1.526590353605009</v>
+      </c>
       <c r="F31">
         <v>0.6071251522102397</v>
       </c>
@@ -9290,6 +9836,9 @@
       <c r="H31">
         <v>1.23023411619943</v>
       </c>
+      <c r="I31">
+        <v>0.7292051952075838</v>
+      </c>
       <c r="J31">
         <v>1.159920542229745</v>
       </c>
@@ -9306,7 +9855,10 @@
         <v>1.739538513521424</v>
       </c>
       <c r="O31">
-        <v>1.297517633636079</v>
+        <v>1.221984365872963</v>
+      </c>
+      <c r="P31">
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>25</v>
@@ -9314,6 +9866,9 @@
       <c r="R31">
         <v>34</v>
       </c>
+      <c r="S31">
+        <v>46</v>
+      </c>
       <c r="T31">
         <v>26</v>
       </c>
@@ -9323,6 +9878,9 @@
       <c r="V31">
         <v>41</v>
       </c>
+      <c r="W31">
+        <v>17</v>
+      </c>
       <c r="X31">
         <v>39</v>
       </c>
@@ -9339,7 +9897,7 @@
         <v>44</v>
       </c>
       <c r="AC31">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
@@ -9348,12 +9906,18 @@
           <t>New Mexico</t>
         </is>
       </c>
+      <c r="B32">
+        <v>0.9060584231035613</v>
+      </c>
       <c r="C32">
         <v>0.6706945071743736</v>
       </c>
       <c r="D32">
         <v>1.546548735380322</v>
       </c>
+      <c r="E32">
+        <v>1.408554848854871</v>
+      </c>
       <c r="F32">
         <v>2.147443270229993</v>
       </c>
@@ -9363,6 +9927,9 @@
       <c r="H32">
         <v>1.129740539524886</v>
       </c>
+      <c r="I32">
+        <v>1.445592623220356</v>
+      </c>
       <c r="J32">
         <v>1.324183329369569</v>
       </c>
@@ -9379,7 +9946,10 @@
         <v>0.7501223319957364</v>
       </c>
       <c r="O32">
-        <v>1.10489873022502</v>
+        <v>1.139168707494538</v>
+      </c>
+      <c r="P32">
+        <v>20</v>
       </c>
       <c r="Q32">
         <v>13</v>
@@ -9387,6 +9957,9 @@
       <c r="R32">
         <v>35</v>
       </c>
+      <c r="S32">
+        <v>42</v>
+      </c>
       <c r="T32">
         <v>44</v>
       </c>
@@ -9396,6 +9969,9 @@
       <c r="V32">
         <v>40</v>
       </c>
+      <c r="W32">
+        <v>47</v>
+      </c>
       <c r="X32">
         <v>41</v>
       </c>
@@ -9412,7 +9988,7 @@
         <v>26</v>
       </c>
       <c r="AC32">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -9421,12 +9997,18 @@
           <t>New York</t>
         </is>
       </c>
+      <c r="B33">
+        <v>0.8244322300749829</v>
+      </c>
       <c r="C33">
         <v>1.402498498167605</v>
       </c>
       <c r="D33">
         <v>0.9262800385420014</v>
       </c>
+      <c r="E33">
+        <v>0.4911681201793336</v>
+      </c>
       <c r="F33">
         <v>0.7791547734297884</v>
       </c>
@@ -9436,6 +10018,9 @@
       <c r="H33">
         <v>1.867981184888021</v>
       </c>
+      <c r="I33">
+        <v>0.7317859393067448</v>
+      </c>
       <c r="J33">
         <v>2.200459451075125</v>
       </c>
@@ -9452,7 +10037,10 @@
         <v>2.445766596452321</v>
       </c>
       <c r="O33">
-        <v>1.59608740880763</v>
+        <v>1.385250798279797</v>
+      </c>
+      <c r="P33">
+        <v>15</v>
       </c>
       <c r="Q33">
         <v>41</v>
@@ -9460,6 +10048,9 @@
       <c r="R33">
         <v>27</v>
       </c>
+      <c r="S33">
+        <v>4</v>
+      </c>
       <c r="T33">
         <v>33</v>
       </c>
@@ -9469,6 +10060,9 @@
       <c r="V33">
         <v>47</v>
       </c>
+      <c r="W33">
+        <v>18</v>
+      </c>
       <c r="X33">
         <v>48</v>
       </c>
@@ -9485,7 +10079,7 @@
         <v>48</v>
       </c>
       <c r="AC33">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
@@ -9494,12 +10088,18 @@
           <t>North Carolina</t>
         </is>
       </c>
+      <c r="B34">
+        <v>0.98630745697769</v>
+      </c>
       <c r="C34">
         <v>1.004718104899085</v>
       </c>
       <c r="D34">
         <v>0.5186220694597287</v>
       </c>
+      <c r="E34">
+        <v>1.022288788123899</v>
+      </c>
       <c r="F34">
         <v>0.514184530817918</v>
       </c>
@@ -9509,6 +10109,9 @@
       <c r="H34">
         <v>0.3940616950635396</v>
       </c>
+      <c r="I34">
+        <v>0.9283560327768183</v>
+      </c>
       <c r="J34">
         <v>0.56260482586623</v>
       </c>
@@ -9525,7 +10128,10 @@
         <v>0.4109581444227013</v>
       </c>
       <c r="O34">
-        <v>0.5598147303388533</v>
+        <v>0.6565461216359185</v>
+      </c>
+      <c r="P34">
+        <v>30</v>
       </c>
       <c r="Q34">
         <v>31</v>
@@ -9533,6 +10139,9 @@
       <c r="R34">
         <v>18</v>
       </c>
+      <c r="S34">
+        <v>31</v>
+      </c>
       <c r="T34">
         <v>22</v>
       </c>
@@ -9542,6 +10151,9 @@
       <c r="V34">
         <v>12</v>
       </c>
+      <c r="W34">
+        <v>22</v>
+      </c>
       <c r="X34">
         <v>19</v>
       </c>
@@ -9558,7 +10170,7 @@
         <v>12</v>
       </c>
       <c r="AC34">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -9567,12 +10179,18 @@
           <t>North Dakota</t>
         </is>
       </c>
+      <c r="B35">
+        <v>0.7496294294366646</v>
+      </c>
       <c r="C35">
         <v>1.631977687686749</v>
       </c>
       <c r="D35">
         <v>0.5869755332055396</v>
       </c>
+      <c r="E35">
+        <v>0.7731956434389442</v>
+      </c>
       <c r="F35">
         <v>0.2326936116535781</v>
       </c>
@@ -9582,6 +10200,9 @@
       <c r="H35">
         <v>0.5712927097415086</v>
       </c>
+      <c r="I35">
+        <v>0.3438802859526671</v>
+      </c>
       <c r="J35">
         <v>0.06604170553614229</v>
       </c>
@@ -9598,7 +10219,10 @@
         <v>0.7509879344493596</v>
       </c>
       <c r="O35">
-        <v>0.5998378389308298</v>
+        <v>0.6050064421643518</v>
+      </c>
+      <c r="P35">
+        <v>11</v>
       </c>
       <c r="Q35">
         <v>42</v>
@@ -9606,6 +10230,9 @@
       <c r="R35">
         <v>21</v>
       </c>
+      <c r="S35">
+        <v>14</v>
+      </c>
       <c r="T35">
         <v>10</v>
       </c>
@@ -9615,6 +10242,9 @@
       <c r="V35">
         <v>19</v>
       </c>
+      <c r="W35">
+        <v>1</v>
+      </c>
       <c r="X35">
         <v>2</v>
       </c>
@@ -9631,7 +10261,7 @@
         <v>27</v>
       </c>
       <c r="AC35">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -9640,12 +10270,18 @@
           <t>Ohio</t>
         </is>
       </c>
+      <c r="B36">
+        <v>0.9296536275909441</v>
+      </c>
       <c r="C36">
         <v>0.7048404252615226</v>
       </c>
       <c r="D36">
         <v>0.4390426452245062</v>
       </c>
+      <c r="E36">
+        <v>0.5813132049875491</v>
+      </c>
       <c r="F36">
         <v>0.4859053617727038</v>
       </c>
@@ -9655,6 +10291,9 @@
       <c r="H36">
         <v>0.9805053347674334</v>
       </c>
+      <c r="I36">
+        <v>0.7163251931921798</v>
+      </c>
       <c r="J36">
         <v>0.7307101165483832</v>
       </c>
@@ -9671,7 +10310,10 @@
         <v>0.4680229830217069</v>
       </c>
       <c r="O36">
-        <v>0.6072750906716911</v>
+        <v>0.6384648409605833</v>
+      </c>
+      <c r="P36">
+        <v>26</v>
       </c>
       <c r="Q36">
         <v>17</v>
@@ -9679,6 +10321,9 @@
       <c r="R36">
         <v>15</v>
       </c>
+      <c r="S36">
+        <v>9</v>
+      </c>
       <c r="T36">
         <v>20</v>
       </c>
@@ -9688,6 +10333,9 @@
       <c r="V36">
         <v>36</v>
       </c>
+      <c r="W36">
+        <v>15</v>
+      </c>
       <c r="X36">
         <v>25</v>
       </c>
@@ -9704,7 +10352,7 @@
         <v>15</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -9713,12 +10361,18 @@
           <t>Oklahoma</t>
         </is>
       </c>
+      <c r="B37">
+        <v>1.30580864346613</v>
+      </c>
       <c r="C37">
         <v>1.144557766631165</v>
       </c>
       <c r="D37">
         <v>2.080421926662737</v>
       </c>
+      <c r="E37">
+        <v>0.8318615128518986</v>
+      </c>
       <c r="F37">
         <v>0.8679415792230573</v>
       </c>
@@ -9728,6 +10382,9 @@
       <c r="H37">
         <v>0.7894518983352597</v>
       </c>
+      <c r="I37">
+        <v>1.117031646907113</v>
+      </c>
       <c r="J37">
         <v>1.103159273498292</v>
       </c>
@@ -9744,7 +10401,10 @@
         <v>1.402053986637626</v>
       </c>
       <c r="O37">
-        <v>1.31260317034068</v>
+        <v>1.260056423587073</v>
+      </c>
+      <c r="P37">
+        <v>44</v>
       </c>
       <c r="Q37">
         <v>35</v>
@@ -9752,6 +10412,9 @@
       <c r="R37">
         <v>44</v>
       </c>
+      <c r="S37">
+        <v>21</v>
+      </c>
       <c r="T37">
         <v>34</v>
       </c>
@@ -9761,6 +10424,9 @@
       <c r="V37">
         <v>29</v>
       </c>
+      <c r="W37">
+        <v>37</v>
+      </c>
       <c r="X37">
         <v>37</v>
       </c>
@@ -9777,7 +10443,7 @@
         <v>40</v>
       </c>
       <c r="AC37">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38">
@@ -9786,12 +10452,18 @@
           <t>Oregon</t>
         </is>
       </c>
+      <c r="B38">
+        <v>1.12166667189448</v>
+      </c>
       <c r="C38">
         <v>0.6857345600490986</v>
       </c>
       <c r="D38">
         <v>0.3936379736038624</v>
       </c>
+      <c r="E38">
+        <v>1.454427717839401</v>
+      </c>
       <c r="F38">
         <v>0.2442738548810911</v>
       </c>
@@ -9801,6 +10473,9 @@
       <c r="H38">
         <v>0.7452610877930345</v>
       </c>
+      <c r="I38">
+        <v>1.083288654589849</v>
+      </c>
       <c r="J38">
         <v>0.5571415591091499</v>
       </c>
@@ -9817,7 +10492,10 @@
         <v>1.285619247835468</v>
       </c>
       <c r="O38">
-        <v>0.8159547742171458</v>
+        <v>0.9091485220380914</v>
+      </c>
+      <c r="P38">
+        <v>38</v>
       </c>
       <c r="Q38">
         <v>15</v>
@@ -9825,6 +10503,9 @@
       <c r="R38">
         <v>13</v>
       </c>
+      <c r="S38">
+        <v>44</v>
+      </c>
       <c r="T38">
         <v>12</v>
       </c>
@@ -9834,6 +10515,9 @@
       <c r="V38">
         <v>27</v>
       </c>
+      <c r="W38">
+        <v>34</v>
+      </c>
       <c r="X38">
         <v>18</v>
       </c>
@@ -9850,7 +10534,7 @@
         <v>38</v>
       </c>
       <c r="AC38">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
@@ -9859,12 +10543,18 @@
           <t>Pennsylvania</t>
         </is>
       </c>
+      <c r="B39">
+        <v>1.10673535631864</v>
+      </c>
       <c r="C39">
         <v>1.871214547826957</v>
       </c>
       <c r="D39">
         <v>1.302544402056047</v>
       </c>
+      <c r="E39">
+        <v>0.5050376456501077</v>
+      </c>
       <c r="F39">
         <v>0.9623708124269743</v>
       </c>
@@ -9874,6 +10564,9 @@
       <c r="H39">
         <v>1.039929629360226</v>
       </c>
+      <c r="I39">
+        <v>1.061792018844983</v>
+      </c>
       <c r="J39">
         <v>1.404796235942467</v>
       </c>
@@ -9890,7 +10583,10 @@
         <v>1.153196537384685</v>
       </c>
       <c r="O39">
-        <v>1.097762503514311</v>
+        <v>1.050091542765911</v>
+      </c>
+      <c r="P39">
+        <v>35</v>
       </c>
       <c r="Q39">
         <v>45</v>
@@ -9898,6 +10594,9 @@
       <c r="R39">
         <v>33</v>
       </c>
+      <c r="S39">
+        <v>6</v>
+      </c>
       <c r="T39">
         <v>39</v>
       </c>
@@ -9907,6 +10606,9 @@
       <c r="V39">
         <v>39</v>
       </c>
+      <c r="W39">
+        <v>30</v>
+      </c>
       <c r="X39">
         <v>43</v>
       </c>
@@ -9932,12 +10634,18 @@
           <t>Rhode Island</t>
         </is>
       </c>
+      <c r="B40">
+        <v>0.6412419700794157</v>
+      </c>
       <c r="C40">
         <v>2.259862939366645</v>
       </c>
       <c r="D40">
         <v>4.855515006617974</v>
       </c>
+      <c r="E40">
+        <v>0.4975937089671547</v>
+      </c>
       <c r="F40">
         <v>0</v>
       </c>
@@ -9947,6 +10655,9 @@
       <c r="H40">
         <v>1.979573323621126</v>
       </c>
+      <c r="I40">
+        <v>0.524496507859315</v>
+      </c>
       <c r="J40">
         <v>0.1608284295981063</v>
       </c>
@@ -9963,7 +10674,10 @@
         <v>0.3159952712315088</v>
       </c>
       <c r="O40">
-        <v>1.255554207358071</v>
+        <v>1.093759558498969</v>
+      </c>
+      <c r="P40">
+        <v>4</v>
       </c>
       <c r="Q40">
         <v>46</v>
@@ -9971,6 +10685,9 @@
       <c r="R40">
         <v>49</v>
       </c>
+      <c r="S40">
+        <v>5</v>
+      </c>
       <c r="T40">
         <v>1</v>
       </c>
@@ -9980,6 +10697,9 @@
       <c r="V40">
         <v>48</v>
       </c>
+      <c r="W40">
+        <v>4</v>
+      </c>
       <c r="X40">
         <v>4</v>
       </c>
@@ -9996,7 +10716,7 @@
         <v>6</v>
       </c>
       <c r="AC40">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -10005,12 +10725,18 @@
           <t>South Carolina</t>
         </is>
       </c>
+      <c r="B41">
+        <v>1.319554659544971</v>
+      </c>
       <c r="C41">
         <v>0.9181810055459642</v>
       </c>
       <c r="D41">
         <v>0.5750700015968063</v>
       </c>
+      <c r="E41">
+        <v>1.505587976077368</v>
+      </c>
       <c r="F41">
         <v>0.5668821938130079</v>
       </c>
@@ -10020,6 +10746,9 @@
       <c r="H41">
         <v>0.212530599588442</v>
       </c>
+      <c r="I41">
+        <v>1.364233151056419</v>
+      </c>
       <c r="J41">
         <v>0.5975888047625311</v>
       </c>
@@ -10036,7 +10765,10 @@
         <v>0.009339233094551768</v>
       </c>
       <c r="O41">
-        <v>0.4355165768892297</v>
+        <v>0.6572724273516196</v>
+      </c>
+      <c r="P41">
+        <v>45</v>
       </c>
       <c r="Q41">
         <v>27</v>
@@ -10044,6 +10776,9 @@
       <c r="R41">
         <v>20</v>
       </c>
+      <c r="S41">
+        <v>45</v>
+      </c>
       <c r="T41">
         <v>24</v>
       </c>
@@ -10053,6 +10788,9 @@
       <c r="V41">
         <v>5</v>
       </c>
+      <c r="W41">
+        <v>46</v>
+      </c>
       <c r="X41">
         <v>21</v>
       </c>
@@ -10069,7 +10807,7 @@
         <v>1</v>
       </c>
       <c r="AC41">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -10078,12 +10816,18 @@
           <t>South Dakota</t>
         </is>
       </c>
+      <c r="B42">
+        <v>1.396585599987767</v>
+      </c>
       <c r="C42">
         <v>2.432367276005801</v>
       </c>
       <c r="D42">
         <v>0.7558649544877212</v>
       </c>
+      <c r="E42">
+        <v>0.9344638839653246</v>
+      </c>
       <c r="F42">
         <v>0.151481846373294</v>
       </c>
@@ -10093,6 +10837,9 @@
       <c r="H42">
         <v>0.5646491008120046</v>
       </c>
+      <c r="I42">
+        <v>0.5409509730267414</v>
+      </c>
       <c r="J42">
         <v>0.3773530165900005</v>
       </c>
@@ -10109,7 +10856,10 @@
         <v>0.8440146386040174</v>
       </c>
       <c r="O42">
-        <v>0.8952831998637082</v>
+        <v>0.9096024965859165</v>
+      </c>
+      <c r="P42">
+        <v>47</v>
       </c>
       <c r="Q42">
         <v>48</v>
@@ -10117,6 +10867,9 @@
       <c r="R42">
         <v>24</v>
       </c>
+      <c r="S42">
+        <v>27</v>
+      </c>
       <c r="T42">
         <v>7</v>
       </c>
@@ -10126,6 +10879,9 @@
       <c r="V42">
         <v>18</v>
       </c>
+      <c r="W42">
+        <v>5</v>
+      </c>
       <c r="X42">
         <v>10</v>
       </c>
@@ -10142,7 +10898,7 @@
         <v>29</v>
       </c>
       <c r="AC42">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -10215,7 +10971,7 @@
         <v>2</v>
       </c>
       <c r="AC43">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -10224,12 +10980,18 @@
           <t>Texas</t>
         </is>
       </c>
+      <c r="B44">
+        <v>1.188612903083</v>
+      </c>
       <c r="C44">
         <v>0.1821698820855988</v>
       </c>
       <c r="D44">
         <v>0.4554971984010375</v>
       </c>
+      <c r="E44">
+        <v>1.162397589370366</v>
+      </c>
       <c r="F44">
         <v>0.4824333801844599</v>
       </c>
@@ -10239,6 +11001,9 @@
       <c r="H44">
         <v>0.9880749601118354</v>
       </c>
+      <c r="I44">
+        <v>1.075943617286769</v>
+      </c>
       <c r="J44">
         <v>1.00257693381607</v>
       </c>
@@ -10255,7 +11020,10 @@
         <v>1.366707406314812</v>
       </c>
       <c r="O44">
-        <v>0.876725572858115</v>
+        <v>0.9380161414093297</v>
+      </c>
+      <c r="P44">
+        <v>41</v>
       </c>
       <c r="Q44">
         <v>3</v>
@@ -10263,6 +11031,9 @@
       <c r="R44">
         <v>16</v>
       </c>
+      <c r="S44">
+        <v>37</v>
+      </c>
       <c r="T44">
         <v>19</v>
       </c>
@@ -10272,6 +11043,9 @@
       <c r="V44">
         <v>37</v>
       </c>
+      <c r="W44">
+        <v>33</v>
+      </c>
       <c r="X44">
         <v>32</v>
       </c>
@@ -10288,7 +11062,7 @@
         <v>39</v>
       </c>
       <c r="AC44">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45">
@@ -10297,12 +11071,18 @@
           <t>Utah</t>
         </is>
       </c>
+      <c r="B45">
+        <v>0.5581166618578144</v>
+      </c>
       <c r="C45">
         <v>0.4330003738317756</v>
       </c>
       <c r="D45">
         <v>0.2614532931323879</v>
       </c>
+      <c r="E45">
+        <v>1.025718291049169</v>
+      </c>
       <c r="F45">
         <v>0.2288623133913589</v>
       </c>
@@ -10312,6 +11092,9 @@
       <c r="H45">
         <v>0.2127317224393538</v>
       </c>
+      <c r="I45">
+        <v>0.5748306489580042</v>
+      </c>
       <c r="J45">
         <v>0.5452004439862309</v>
       </c>
@@ -10328,7 +11111,10 @@
         <v>1.028794854312139</v>
       </c>
       <c r="O45">
-        <v>0.6021493840283746</v>
+        <v>0.6292430340114411</v>
+      </c>
+      <c r="P45">
+        <v>3</v>
       </c>
       <c r="Q45">
         <v>8</v>
@@ -10336,6 +11122,9 @@
       <c r="R45">
         <v>7</v>
       </c>
+      <c r="S45">
+        <v>32</v>
+      </c>
       <c r="T45">
         <v>9</v>
       </c>
@@ -10345,6 +11134,9 @@
       <c r="V45">
         <v>6</v>
       </c>
+      <c r="W45">
+        <v>7</v>
+      </c>
       <c r="X45">
         <v>17</v>
       </c>
@@ -10361,7 +11153,7 @@
         <v>34</v>
       </c>
       <c r="AC45">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -10370,12 +11162,18 @@
           <t>Vermont</t>
         </is>
       </c>
+      <c r="B46">
+        <v>0.6868394189876488</v>
+      </c>
       <c r="C46">
         <v>0.4312264226300551</v>
       </c>
       <c r="D46">
         <v>1.795922227469368</v>
       </c>
+      <c r="E46">
+        <v>0.4699085794972739</v>
+      </c>
       <c r="F46">
         <v>0.4243113561860449</v>
       </c>
@@ -10385,6 +11183,9 @@
       <c r="H46">
         <v>0.7270227052228045</v>
       </c>
+      <c r="I46">
+        <v>0.5923456769499468</v>
+      </c>
       <c r="J46">
         <v>0.1670948929463442</v>
       </c>
@@ -10401,7 +11202,10 @@
         <v>2.019732927744569</v>
       </c>
       <c r="O46">
-        <v>1.342072817732619</v>
+        <v>1.166909373289312</v>
+      </c>
+      <c r="P46">
+        <v>8</v>
       </c>
       <c r="Q46">
         <v>7</v>
@@ -10409,6 +11213,9 @@
       <c r="R46">
         <v>39</v>
       </c>
+      <c r="S46">
+        <v>2</v>
+      </c>
       <c r="T46">
         <v>16</v>
       </c>
@@ -10418,6 +11225,9 @@
       <c r="V46">
         <v>26</v>
       </c>
+      <c r="W46">
+        <v>8</v>
+      </c>
       <c r="X46">
         <v>5</v>
       </c>
@@ -10434,7 +11244,7 @@
         <v>46</v>
       </c>
       <c r="AC46">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47">
@@ -10443,12 +11253,18 @@
           <t>Virginia</t>
         </is>
       </c>
+      <c r="B47">
+        <v>0.9194554568706659</v>
+      </c>
       <c r="C47">
         <v>0.5033375655237308</v>
       </c>
       <c r="D47">
         <v>0.5006373644797254</v>
       </c>
+      <c r="E47">
+        <v>1.089093996069861</v>
+      </c>
       <c r="F47">
         <v>0.4907540787728799</v>
       </c>
@@ -10458,6 +11274,9 @@
       <c r="H47">
         <v>0.4720771532035531</v>
       </c>
+      <c r="I47">
+        <v>0.6977012577146793</v>
+      </c>
       <c r="J47">
         <v>0.9460900051729214</v>
       </c>
@@ -10474,7 +11293,10 @@
         <v>0.466758744579316</v>
       </c>
       <c r="O47">
-        <v>0.608369758430112</v>
+        <v>0.6761498688427943</v>
+      </c>
+      <c r="P47">
+        <v>25</v>
       </c>
       <c r="Q47">
         <v>10</v>
@@ -10482,6 +11304,9 @@
       <c r="R47">
         <v>17</v>
       </c>
+      <c r="S47">
+        <v>33</v>
+      </c>
       <c r="T47">
         <v>21</v>
       </c>
@@ -10491,6 +11316,9 @@
       <c r="V47">
         <v>16</v>
       </c>
+      <c r="W47">
+        <v>12</v>
+      </c>
       <c r="X47">
         <v>30</v>
       </c>
@@ -10507,7 +11335,7 @@
         <v>14</v>
       </c>
       <c r="AC47">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -10516,12 +11344,18 @@
           <t>Washington</t>
         </is>
       </c>
+      <c r="B48">
+        <v>1.002455299314826</v>
+      </c>
       <c r="C48">
         <v>0.8106817877562473</v>
       </c>
       <c r="D48">
         <v>1.140330802003307</v>
       </c>
+      <c r="E48">
+        <v>0.9154915662554906</v>
+      </c>
       <c r="F48">
         <v>2.904435073385776</v>
       </c>
@@ -10531,6 +11365,9 @@
       <c r="H48">
         <v>1.505843443730358</v>
       </c>
+      <c r="I48">
+        <v>1.058753472719543</v>
+      </c>
       <c r="J48">
         <v>0.975060570841201</v>
       </c>
@@ -10547,7 +11384,10 @@
         <v>4.884562462193406</v>
       </c>
       <c r="O48">
-        <v>2.05009969127741</v>
+        <v>1.805976711620305</v>
+      </c>
+      <c r="P48">
+        <v>31</v>
       </c>
       <c r="Q48">
         <v>23</v>
@@ -10555,6 +11395,9 @@
       <c r="R48">
         <v>30</v>
       </c>
+      <c r="S48">
+        <v>26</v>
+      </c>
       <c r="T48">
         <v>46</v>
       </c>
@@ -10564,6 +11407,9 @@
       <c r="V48">
         <v>45</v>
       </c>
+      <c r="W48">
+        <v>29</v>
+      </c>
       <c r="X48">
         <v>31</v>
       </c>
@@ -10589,12 +11435,18 @@
           <t>West Virginia</t>
         </is>
       </c>
+      <c r="B49">
+        <v>1.434517247736388</v>
+      </c>
       <c r="C49">
         <v>2.772351675969673</v>
       </c>
       <c r="D49">
         <v>1.891333552300565</v>
       </c>
+      <c r="E49">
+        <v>0.6185189898333322</v>
+      </c>
       <c r="F49">
         <v>0.9124974859722969</v>
       </c>
@@ -10604,6 +11456,9 @@
       <c r="H49">
         <v>0.4646711270866573</v>
       </c>
+      <c r="I49">
+        <v>1.289797039886346</v>
+      </c>
       <c r="J49">
         <v>0.8304050688849586</v>
       </c>
@@ -10620,7 +11475,10 @@
         <v>0.4010302277091328</v>
       </c>
       <c r="O49">
-        <v>0.9325714194860965</v>
+        <v>0.9745036517166947</v>
+      </c>
+      <c r="P49">
+        <v>48</v>
       </c>
       <c r="Q49">
         <v>49</v>
@@ -10628,6 +11486,9 @@
       <c r="R49">
         <v>43</v>
       </c>
+      <c r="S49">
+        <v>10</v>
+      </c>
       <c r="T49">
         <v>37</v>
       </c>
@@ -10637,6 +11498,9 @@
       <c r="V49">
         <v>14</v>
       </c>
+      <c r="W49">
+        <v>44</v>
+      </c>
       <c r="X49">
         <v>29</v>
       </c>
@@ -10653,7 +11517,7 @@
         <v>11</v>
       </c>
       <c r="AC49">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -10662,12 +11526,18 @@
           <t>Wisconsin</t>
         </is>
       </c>
+      <c r="B50">
+        <v>0.8116526760613654</v>
+      </c>
       <c r="C50">
         <v>0.9696169367902057</v>
       </c>
       <c r="D50">
         <v>1.764533859218351</v>
       </c>
+      <c r="E50">
+        <v>0.4262779692535499</v>
+      </c>
       <c r="F50">
         <v>0.6902941379954214</v>
       </c>
@@ -10677,6 +11547,9 @@
       <c r="H50">
         <v>1.500438543700507</v>
       </c>
+      <c r="I50">
+        <v>0.66666884283464</v>
+      </c>
       <c r="J50">
         <v>0.7361909956654326</v>
       </c>
@@ -10693,7 +11566,10 @@
         <v>2.235424562700156</v>
       </c>
       <c r="O50">
-        <v>1.082083541459507</v>
+        <v>0.9788796079034326</v>
+      </c>
+      <c r="P50">
+        <v>13</v>
       </c>
       <c r="Q50">
         <v>29</v>
@@ -10701,6 +11577,9 @@
       <c r="R50">
         <v>38</v>
       </c>
+      <c r="S50">
+        <v>1</v>
+      </c>
       <c r="T50">
         <v>29</v>
       </c>
@@ -10710,6 +11589,9 @@
       <c r="V50">
         <v>44</v>
       </c>
+      <c r="W50">
+        <v>9</v>
+      </c>
       <c r="X50">
         <v>26</v>
       </c>
@@ -10726,7 +11608,7 @@
         <v>47</v>
       </c>
       <c r="AC50">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
@@ -10735,12 +11617,18 @@
           <t>Wyoming</t>
         </is>
       </c>
+      <c r="B51">
+        <v>0.8738354678900174</v>
+      </c>
       <c r="C51">
         <v>0.9672773404832817</v>
       </c>
       <c r="D51">
         <v>0.1486481678661591</v>
       </c>
+      <c r="E51">
+        <v>0.8250067906267997</v>
+      </c>
       <c r="F51">
         <v>0.5828327766094176</v>
       </c>
@@ -10750,6 +11638,9 @@
       <c r="H51">
         <v>0.5766022673643969</v>
       </c>
+      <c r="I51">
+        <v>1.094795888567732</v>
+      </c>
       <c r="J51">
         <v>1.565845671706672</v>
       </c>
@@ -10766,7 +11657,10 @@
         <v>0.4976698025801061</v>
       </c>
       <c r="O51">
-        <v>0.6862226813706762</v>
+        <v>0.7427588431377932</v>
+      </c>
+      <c r="P51">
+        <v>17</v>
       </c>
       <c r="Q51">
         <v>28</v>
@@ -10774,6 +11668,9 @@
       <c r="R51">
         <v>1</v>
       </c>
+      <c r="S51">
+        <v>19</v>
+      </c>
       <c r="T51">
         <v>25</v>
       </c>
@@ -10783,6 +11680,9 @@
       <c r="V51">
         <v>20</v>
       </c>
+      <c r="W51">
+        <v>35</v>
+      </c>
       <c r="X51">
         <v>46</v>
       </c>
@@ -10799,7 +11699,7 @@
         <v>16</v>
       </c>
       <c r="AC51">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/AHR 30th/output/AHR_data 30th.xlsx
+++ b/AHR 30th/output/AHR_data 30th.xlsx
@@ -5833,6 +5833,15 @@
       <c r="U43">
         <v>625</v>
       </c>
+      <c r="V43">
+        <v>16164.75063</v>
+      </c>
+      <c r="W43">
+        <v>31959.74724</v>
+      </c>
+      <c r="X43">
+        <v>30779.92565</v>
+      </c>
       <c r="Y43">
         <v>20379</v>
       </c>
@@ -5875,6 +5884,15 @@
       <c r="AL43">
         <v>4.406496884047304</v>
       </c>
+      <c r="AM43">
+        <v>0.9650628306661357</v>
+      </c>
+      <c r="AN43">
+        <v>1.298508392083266</v>
+      </c>
+      <c r="AO43">
+        <v>2.030544216080652</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6959,13 +6977,13 @@
         <v>20476</v>
       </c>
       <c r="V52">
-        <v>508600.1860000001</v>
+        <v>524764.9366300001</v>
       </c>
       <c r="W52">
-        <v>1289802.93042</v>
+        <v>1321762.67766</v>
       </c>
       <c r="X52">
-        <v>1413184.333949999</v>
+        <v>1443964.2596</v>
       </c>
       <c r="Y52">
         <v>620505</v>
@@ -7010,13 +7028,13 @@
         <v>6.725167403969349</v>
       </c>
       <c r="AM52">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="AN52">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="AO52">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
     </row>
   </sheetData>
@@ -7183,7 +7201,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.950295253754483</v>
+        <v>0.9709932027434547</v>
       </c>
       <c r="C2">
         <v>0.4982504445757104</v>
@@ -7192,7 +7210,7 @@
         <v>0.3473121067993641</v>
       </c>
       <c r="E2">
-        <v>1.343662560004414</v>
+        <v>1.386367951805704</v>
       </c>
       <c r="F2">
         <v>0.7162469410731637</v>
@@ -7204,7 +7222,7 @@
         <v>0.1399375400426623</v>
       </c>
       <c r="I2">
-        <v>1.105390411122654</v>
+        <v>1.132780640519556</v>
       </c>
       <c r="J2">
         <v>0.6689439992988344</v>
@@ -7222,7 +7240,7 @@
         <v>0.2155470273512655</v>
       </c>
       <c r="O2">
-        <v>0.6254319736522431</v>
+        <v>0.6324160944358711</v>
       </c>
       <c r="P2">
         <v>29</v>
@@ -7234,7 +7252,7 @@
         <v>11</v>
       </c>
       <c r="S2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T2">
         <v>30</v>
@@ -7274,7 +7292,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6802945072684946</v>
+        <v>0.6951116927203739</v>
       </c>
       <c r="C3">
         <v>1.173677114643309</v>
@@ -7283,7 +7301,7 @@
         <v>13.39337924689598</v>
       </c>
       <c r="E3">
-        <v>1.665147672023079</v>
+        <v>1.718070768831341</v>
       </c>
       <c r="F3">
         <v>4.926132398160296</v>
@@ -7295,7 +7313,7 @@
         <v>0.4668749420907918</v>
       </c>
       <c r="I3">
-        <v>1.313345288989801</v>
+        <v>1.345888387229848</v>
       </c>
       <c r="J3">
         <v>0.3792932045112647</v>
@@ -7313,7 +7331,7 @@
         <v>0.6516496839366721</v>
       </c>
       <c r="O3">
-        <v>2.190807718224931</v>
+        <v>2.198521824417253</v>
       </c>
       <c r="P3">
         <v>7</v>
@@ -7325,7 +7343,7 @@
         <v>50</v>
       </c>
       <c r="S3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T3">
         <v>49</v>
@@ -7365,7 +7383,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.466319932263327</v>
+        <v>1.498257180228726</v>
       </c>
       <c r="C4">
         <v>0.1717114563025056</v>
@@ -7374,7 +7392,7 @@
         <v>2.321246711943953</v>
       </c>
       <c r="E4">
-        <v>1.249315199954809</v>
+        <v>1.289021966136641</v>
       </c>
       <c r="F4">
         <v>1.554527621050309</v>
@@ -7386,7 +7404,7 @@
         <v>0.6239471128146915</v>
       </c>
       <c r="I4">
-        <v>1.286241530983455</v>
+        <v>1.318113031078773</v>
       </c>
       <c r="J4">
         <v>0.601583770847452</v>
@@ -7404,10 +7422,10 @@
         <v>1.700070249601834</v>
       </c>
       <c r="O4">
-        <v>1.220842598992924</v>
+        <v>1.228805330857735</v>
       </c>
       <c r="P4">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q4">
         <v>2</v>
@@ -7416,7 +7434,7 @@
         <v>46</v>
       </c>
       <c r="S4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T4">
         <v>42</v>
@@ -7446,7 +7464,7 @@
         <v>43</v>
       </c>
       <c r="AC4">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -7456,7 +7474,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.19394953576997</v>
+        <v>1.219954407928531</v>
       </c>
       <c r="C5">
         <v>0.8068553187777977</v>
@@ -7465,7 +7483,7 @@
         <v>0.7434780105210955</v>
       </c>
       <c r="E5">
-        <v>1.556687422880544</v>
+        <v>1.606163346587189</v>
       </c>
       <c r="F5">
         <v>0.9010387909875616</v>
@@ -7477,7 +7495,7 @@
         <v>0.6642285959332423</v>
       </c>
       <c r="I5">
-        <v>1.022647015207217</v>
+        <v>1.04798696393188</v>
       </c>
       <c r="J5">
         <v>1.009822717626607</v>
@@ -7495,7 +7513,7 @@
         <v>0.3167269599855835</v>
       </c>
       <c r="O5">
-        <v>0.8014017842093326</v>
+        <v>0.809157226100861</v>
       </c>
       <c r="P5">
         <v>42</v>
@@ -7507,7 +7525,7 @@
         <v>22</v>
       </c>
       <c r="S5">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="T5">
         <v>36</v>
@@ -7547,7 +7565,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.143708785941803</v>
+        <v>1.16861938716404</v>
       </c>
       <c r="C6">
         <v>0.8784337083399248</v>
@@ -7556,7 +7574,7 @@
         <v>1.858948492856903</v>
       </c>
       <c r="E6">
-        <v>1.006465391999526</v>
+        <v>1.03845370527041</v>
       </c>
       <c r="F6">
         <v>2.756007519587798</v>
@@ -7568,7 +7586,7 @@
         <v>2.426753188717774</v>
       </c>
       <c r="I6">
-        <v>0.9500758615639947</v>
+        <v>0.9736175854027854</v>
       </c>
       <c r="J6">
         <v>1.823141479848573</v>
@@ -7586,7 +7604,7 @@
         <v>1.478503991133346</v>
       </c>
       <c r="O6">
-        <v>1.513355303948671</v>
+        <v>1.519543045358818</v>
       </c>
       <c r="P6">
         <v>39</v>
@@ -7598,7 +7616,7 @@
         <v>41</v>
       </c>
       <c r="S6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T6">
         <v>45</v>
@@ -7638,7 +7656,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.8916396646265115</v>
+        <v>0.9110600628891249</v>
       </c>
       <c r="C7">
         <v>0.7165233596745549</v>
@@ -7647,7 +7665,7 @@
         <v>1.750307216898924</v>
       </c>
       <c r="E7">
-        <v>1.150265683737659</v>
+        <v>1.186824376494145</v>
       </c>
       <c r="F7">
         <v>3.530626951776008</v>
@@ -7659,7 +7677,7 @@
         <v>0.9588068257021187</v>
       </c>
       <c r="I7">
-        <v>1.240347254674201</v>
+        <v>1.271081550444724</v>
       </c>
       <c r="J7">
         <v>1.562052877917234</v>
@@ -7677,7 +7695,7 @@
         <v>0.9739404538803551</v>
       </c>
       <c r="O7">
-        <v>1.295339098042109</v>
+        <v>1.302009358564387</v>
       </c>
       <c r="P7">
         <v>18</v>
@@ -7689,7 +7707,7 @@
         <v>37</v>
       </c>
       <c r="S7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T7">
         <v>48</v>
@@ -7729,7 +7747,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>1.002893870613157</v>
+        <v>1.024737446168535</v>
       </c>
       <c r="C8">
         <v>0.7017458823413153</v>
@@ -7738,7 +7756,7 @@
         <v>1.797467721193777</v>
       </c>
       <c r="E8">
-        <v>0.484274446768833</v>
+        <v>0.4996660566895171</v>
       </c>
       <c r="F8">
         <v>0.01538557866241582</v>
@@ -7750,7 +7768,7 @@
         <v>0.6526821733681566</v>
       </c>
       <c r="I8">
-        <v>0.7493129479775652</v>
+        <v>0.7678800110972188</v>
       </c>
       <c r="J8">
         <v>0.3921757957905561</v>
@@ -7768,7 +7786,7 @@
         <v>0.6957518110705576</v>
       </c>
       <c r="O8">
-        <v>0.6817215783064283</v>
+        <v>0.6860140589676373</v>
       </c>
       <c r="P8">
         <v>32</v>
@@ -7810,7 +7828,7 @@
         <v>25</v>
       </c>
       <c r="AC8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -7820,7 +7838,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>1.117822782681775</v>
+        <v>1.142169572632844</v>
       </c>
       <c r="C9">
         <v>0.1875741991439067</v>
@@ -7829,7 +7847,7 @@
         <v>0.2756647948628159</v>
       </c>
       <c r="E9">
-        <v>0.8197293018064832</v>
+        <v>0.8457826146297031</v>
       </c>
       <c r="G9">
         <v>1.691024825583768</v>
@@ -7838,7 +7856,7 @@
         <v>0.4122126920757007</v>
       </c>
       <c r="I9">
-        <v>1.032132977934284</v>
+        <v>1.05770797727322</v>
       </c>
       <c r="J9">
         <v>1.323094096015478</v>
@@ -7856,7 +7874,7 @@
         <v>0.8753044311214823</v>
       </c>
       <c r="O9">
-        <v>0.9710446559486414</v>
+        <v>0.9773759144580767</v>
       </c>
       <c r="P9">
         <v>37</v>
@@ -7905,7 +7923,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.8229960999016175</v>
+        <v>0.8409214038811818</v>
       </c>
       <c r="C10">
         <v>0.4151967377184102</v>
@@ -7914,7 +7932,7 @@
         <v>0.2284037734916452</v>
       </c>
       <c r="E10">
-        <v>1.342469430930725</v>
+        <v>1.385136901719643</v>
       </c>
       <c r="F10">
         <v>0.1346739857851094</v>
@@ -7926,7 +7944,7 @@
         <v>0.1880272757140078</v>
       </c>
       <c r="I10">
-        <v>1.223968922866506</v>
+        <v>1.254297383503272</v>
       </c>
       <c r="J10">
         <v>0.2407397819349428</v>
@@ -7944,7 +7962,7 @@
         <v>0.4229156193981897</v>
       </c>
       <c r="O10">
-        <v>0.6908135744849813</v>
+        <v>0.6978075156700003</v>
       </c>
       <c r="P10">
         <v>14</v>
@@ -7956,7 +7974,7 @@
         <v>6</v>
       </c>
       <c r="S10">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -7986,7 +8004,7 @@
         <v>13</v>
       </c>
       <c r="AC10">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -7996,7 +8014,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9188428944802592</v>
+        <v>0.9388557939277661</v>
       </c>
       <c r="C11">
         <v>0.2368229079376493</v>
@@ -8005,7 +8023,7 @@
         <v>0.1609624012231248</v>
       </c>
       <c r="E11">
-        <v>0.7216986874631109</v>
+        <v>0.7446363104407784</v>
       </c>
       <c r="F11">
         <v>0.4155847227491939</v>
@@ -8017,7 +8035,7 @@
         <v>0.1345364403216295</v>
       </c>
       <c r="I11">
-        <v>1.073611067757111</v>
+        <v>1.100213843693129</v>
       </c>
       <c r="J11">
         <v>0.3453856511779232</v>
@@ -8035,7 +8053,7 @@
         <v>0.3780956870288102</v>
       </c>
       <c r="O11">
-        <v>0.6295827886754196</v>
+        <v>0.6349330423955113</v>
       </c>
       <c r="P11">
         <v>24</v>
@@ -8087,7 +8105,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.4683796472996711</v>
+        <v>0.4785812115071946</v>
       </c>
       <c r="C12">
         <v>0.9705627028506626</v>
@@ -8096,7 +8114,7 @@
         <v>3.95296086147177</v>
       </c>
       <c r="E12">
-        <v>2.730846823079459</v>
+        <v>2.817640849347879</v>
       </c>
       <c r="F12">
         <v>3.433092135917911</v>
@@ -8108,7 +8126,7 @@
         <v>1.024243729869131</v>
       </c>
       <c r="I12">
-        <v>1.190882996942366</v>
+        <v>1.22039162859224</v>
       </c>
       <c r="J12">
         <v>3.786928095577968</v>
@@ -8126,7 +8144,7 @@
         <v>0.3065714900436239</v>
       </c>
       <c r="O12">
-        <v>1.545549691383753</v>
+        <v>1.555280785393431</v>
       </c>
       <c r="P12">
         <v>2</v>
@@ -8138,7 +8156,7 @@
         <v>48</v>
       </c>
       <c r="S12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T12">
         <v>47</v>
@@ -8178,7 +8196,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.8924530095274993</v>
+        <v>0.9118911228857154</v>
       </c>
       <c r="C13">
         <v>0.7280136791729949</v>
@@ -8187,7 +8205,7 @@
         <v>0.8587414215994613</v>
       </c>
       <c r="E13">
-        <v>1.237232206996926</v>
+        <v>1.276554941529921</v>
       </c>
       <c r="F13">
         <v>0.4811921118629402</v>
@@ -8199,7 +8217,7 @@
         <v>0.9454795402431234</v>
       </c>
       <c r="I13">
-        <v>0.6973193688230925</v>
+        <v>0.7145980943148119</v>
       </c>
       <c r="J13">
         <v>0.4020466045449957</v>
@@ -8217,7 +8235,7 @@
         <v>1.067121333690954</v>
       </c>
       <c r="O13">
-        <v>0.8687778439402162</v>
+        <v>0.8746270418927493</v>
       </c>
       <c r="P13">
         <v>19</v>
@@ -8229,7 +8247,7 @@
         <v>26</v>
       </c>
       <c r="S13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T13">
         <v>18</v>
@@ -8269,7 +8287,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9124938913242251</v>
+        <v>0.9323685060197717</v>
       </c>
       <c r="C14">
         <v>1.389875877970298</v>
@@ -8278,7 +8296,7 @@
         <v>2.271721609045647</v>
       </c>
       <c r="E14">
-        <v>0.8308448204918795</v>
+        <v>0.8572514158985873</v>
       </c>
       <c r="F14">
         <v>0.6529803823467585</v>
@@ -8290,7 +8308,7 @@
         <v>0.8781608144151217</v>
       </c>
       <c r="I14">
-        <v>1.011326084198319</v>
+        <v>1.036385514027396</v>
       </c>
       <c r="J14">
         <v>1.055859294650753</v>
@@ -8308,7 +8326,7 @@
         <v>0.9693590631197845</v>
       </c>
       <c r="O14">
-        <v>1.069212525403705</v>
+        <v>1.074700266936885</v>
       </c>
       <c r="P14">
         <v>22</v>
@@ -8360,7 +8378,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.7099152952082147</v>
+        <v>0.7253776375788172</v>
       </c>
       <c r="C15">
         <v>0.7764642042633283</v>
@@ -8369,7 +8387,7 @@
         <v>0.3197317837348382</v>
       </c>
       <c r="E15">
-        <v>0.9053842169575864</v>
+        <v>0.9341598849465423</v>
       </c>
       <c r="F15">
         <v>1.419707906733865</v>
@@ -8381,7 +8399,7 @@
         <v>0.2176702867692597</v>
       </c>
       <c r="I15">
-        <v>0.7165089607640709</v>
+        <v>0.7342631809950314</v>
       </c>
       <c r="J15">
         <v>1.017754487455121</v>
@@ -8399,7 +8417,7 @@
         <v>0.2026709050837961</v>
       </c>
       <c r="O15">
-        <v>0.8860644750834686</v>
+        <v>0.8908331082058163</v>
       </c>
       <c r="P15">
         <v>10</v>
@@ -8411,7 +8429,7 @@
         <v>10</v>
       </c>
       <c r="S15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T15">
         <v>41</v>
@@ -8451,7 +8469,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.09286770924452</v>
+        <v>1.116670964083759</v>
       </c>
       <c r="C16">
         <v>2.84864839585236</v>
@@ -8460,7 +8478,7 @@
         <v>1.601204011308867</v>
       </c>
       <c r="E16">
-        <v>0.5572152520651036</v>
+        <v>0.5749251268248918</v>
       </c>
       <c r="F16">
         <v>0.8709895404728789</v>
@@ -8472,7 +8490,7 @@
         <v>0.6791801153171246</v>
       </c>
       <c r="I16">
-        <v>0.6744555320784841</v>
+        <v>0.6911677195153888</v>
       </c>
       <c r="J16">
         <v>0.7578249422861457</v>
@@ -8490,7 +8508,7 @@
         <v>0.5774957165281422</v>
       </c>
       <c r="O16">
-        <v>0.9959142193714471</v>
+        <v>1.000393089912673</v>
       </c>
       <c r="P16">
         <v>34</v>
@@ -8542,7 +8560,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.9107626567351403</v>
+        <v>0.9305995641969917</v>
       </c>
       <c r="C17">
         <v>0.7824804778298806</v>
@@ -8551,7 +8569,7 @@
         <v>0.3560492868934582</v>
       </c>
       <c r="E17">
-        <v>0.809357599602629</v>
+        <v>0.8350812704313139</v>
       </c>
       <c r="F17">
         <v>0.2422079025203656</v>
@@ -8563,7 +8581,7 @@
         <v>0.5219836391279373</v>
       </c>
       <c r="I17">
-        <v>0.6991019231996349</v>
+        <v>0.7164248182198708</v>
       </c>
       <c r="J17">
         <v>0.580117266099155</v>
@@ -8581,7 +8599,7 @@
         <v>3.679793821809112</v>
       </c>
       <c r="O17">
-        <v>0.9392927939359724</v>
+        <v>0.9441299841906472</v>
       </c>
       <c r="P17">
         <v>21</v>
@@ -8623,7 +8641,7 @@
         <v>49</v>
       </c>
       <c r="AC17">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -8633,7 +8651,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.340443518757872</v>
+        <v>1.369639109774699</v>
       </c>
       <c r="C18">
         <v>1.095691755021232</v>
@@ -8642,7 +8660,7 @@
         <v>0.2129813341281091</v>
       </c>
       <c r="E18">
-        <v>0.8893343460441584</v>
+        <v>0.9175999037970177</v>
       </c>
       <c r="F18">
         <v>0.4143413379172157</v>
@@ -8654,7 +8672,7 @@
         <v>0.2430269471965881</v>
       </c>
       <c r="I18">
-        <v>1.006227683956952</v>
+        <v>1.031160781631558</v>
       </c>
       <c r="J18">
         <v>1.01765876910368</v>
@@ -8672,7 +8690,7 @@
         <v>0.6780783992328946</v>
       </c>
       <c r="O18">
-        <v>0.6944866668541215</v>
+        <v>0.7008246858113748</v>
       </c>
       <c r="P18">
         <v>46</v>
@@ -8684,7 +8702,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T18">
         <v>14</v>
@@ -8714,7 +8732,7 @@
         <v>24</v>
       </c>
       <c r="AC18">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -8724,7 +8742,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.113452289729006</v>
+        <v>1.137703887959569</v>
       </c>
       <c r="C19">
         <v>1.707336409533238</v>
@@ -8733,7 +8751,7 @@
         <v>2.986195599792868</v>
       </c>
       <c r="E19">
-        <v>0.8420013247354865</v>
+        <v>0.8687625053625003</v>
       </c>
       <c r="F19">
         <v>1.795872724591548</v>
@@ -8745,7 +8763,7 @@
         <v>1.267565002683829</v>
       </c>
       <c r="I19">
-        <v>1.2489285771852</v>
+        <v>1.279875507686167</v>
       </c>
       <c r="J19">
         <v>2.726482932022324</v>
@@ -8763,7 +8781,7 @@
         <v>0.3829849766430218</v>
       </c>
       <c r="O19">
-        <v>1.279414133936146</v>
+        <v>1.285718726963726</v>
       </c>
       <c r="P19">
         <v>36</v>
@@ -8775,7 +8793,7 @@
         <v>47</v>
       </c>
       <c r="S19">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T19">
         <v>43</v>
@@ -8815,7 +8833,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.9484639694737076</v>
+        <v>0.9691220320921243</v>
       </c>
       <c r="C20">
         <v>2.291252229097871</v>
@@ -8824,7 +8842,7 @@
         <v>1.885779083025577</v>
       </c>
       <c r="E20">
-        <v>0.9363392785887356</v>
+        <v>0.9660987858797161</v>
       </c>
       <c r="F20">
         <v>0.0885183705700481</v>
@@ -8836,7 +8854,7 @@
         <v>0.7543100415613085</v>
       </c>
       <c r="I20">
-        <v>0.5235715873475935</v>
+        <v>0.5365450542230532</v>
       </c>
       <c r="J20">
         <v>0.09959238850761926</v>
@@ -8854,7 +8872,7 @@
         <v>0.6198820721727675</v>
       </c>
       <c r="O20">
-        <v>0.8455741415718212</v>
+        <v>0.8504503751706564</v>
       </c>
       <c r="P20">
         <v>28</v>
@@ -8866,7 +8884,7 @@
         <v>42</v>
       </c>
       <c r="S20">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T20">
         <v>4</v>
@@ -8906,7 +8924,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.7705075259201506</v>
+        <v>0.7872896001271995</v>
       </c>
       <c r="C21">
         <v>0.6778591508084953</v>
@@ -8915,7 +8933,7 @@
         <v>0.9297187348564605</v>
       </c>
       <c r="E21">
-        <v>0.5194333980208908</v>
+        <v>0.535942458731107</v>
       </c>
       <c r="F21">
         <v>0.6695223755510638</v>
@@ -8927,7 +8945,7 @@
         <v>1.401001582625498</v>
       </c>
       <c r="I21">
-        <v>1.052742060076994</v>
+        <v>1.078827727395196</v>
       </c>
       <c r="J21">
         <v>1.514256209933429</v>
@@ -8945,7 +8963,7 @@
         <v>1.538742023810754</v>
       </c>
       <c r="O21">
-        <v>1.053275765633974</v>
+        <v>1.057843211959779</v>
       </c>
       <c r="P21">
         <v>12</v>
@@ -8997,7 +9015,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.4547831906943969</v>
+        <v>0.4646886166605317</v>
       </c>
       <c r="C22">
         <v>1.319613598206858</v>
@@ -9006,7 +9024,7 @@
         <v>0.1857955021365204</v>
       </c>
       <c r="E22">
-        <v>0.6450663277860074</v>
+        <v>0.6655683578982627</v>
       </c>
       <c r="F22">
         <v>0.724303678241536</v>
@@ -9018,7 +9036,7 @@
         <v>1.550210486857843</v>
       </c>
       <c r="I22">
-        <v>0.5448775822963089</v>
+        <v>0.5583789858023948</v>
       </c>
       <c r="J22">
         <v>0.6728119505155246</v>
@@ -9036,7 +9054,7 @@
         <v>0.5929257361091261</v>
       </c>
       <c r="O22">
-        <v>0.8863142647650311</v>
+        <v>0.8896918693484523</v>
       </c>
       <c r="P22">
         <v>1</v>
@@ -9078,7 +9096,7 @@
         <v>21</v>
       </c>
       <c r="AC22">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -9088,7 +9106,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.944019525339535</v>
+        <v>0.9645807855403769</v>
       </c>
       <c r="C23">
         <v>1.675125581168334</v>
@@ -9097,7 +9115,7 @@
         <v>0.524930647902506</v>
       </c>
       <c r="E23">
-        <v>0.7059485463342907</v>
+        <v>0.7283855853351079</v>
       </c>
       <c r="F23">
         <v>1.019248878529075</v>
@@ -9109,7 +9127,7 @@
         <v>0.8661395356055072</v>
       </c>
       <c r="I23">
-        <v>0.8809362528146218</v>
+        <v>0.9027647812746559</v>
       </c>
       <c r="J23">
         <v>1.332849633143921</v>
@@ -9127,7 +9145,7 @@
         <v>0.5471764420604555</v>
       </c>
       <c r="O23">
-        <v>0.8484520163939521</v>
+        <v>0.8534386954448515</v>
       </c>
       <c r="P23">
         <v>27</v>
@@ -9179,7 +9197,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.6728656307420843</v>
+        <v>0.6875210112109528</v>
       </c>
       <c r="C24">
         <v>0.6604035262794286</v>
@@ -9188,7 +9206,7 @@
         <v>0.7453603100308376</v>
       </c>
       <c r="E24">
-        <v>0.7800221010168312</v>
+        <v>0.8048134068320945</v>
       </c>
       <c r="F24">
         <v>0.1984027485362007</v>
@@ -9200,7 +9218,7 @@
         <v>0.1292740488965809</v>
       </c>
       <c r="I24">
-        <v>0.3651674964875611</v>
+        <v>0.3742159027306805</v>
       </c>
       <c r="J24">
         <v>0.397867068708741</v>
@@ -9218,7 +9236,7 @@
         <v>1.855265144785831</v>
       </c>
       <c r="O24">
-        <v>0.7602517282194614</v>
+        <v>0.7639821199523269</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -9260,7 +9278,7 @@
         <v>45</v>
       </c>
       <c r="AC24">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
@@ -9270,7 +9288,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>1.301650769842206</v>
+        <v>1.330001433627179</v>
       </c>
       <c r="C25">
         <v>0.8963106515995202</v>
@@ -9279,7 +9297,7 @@
         <v>1.144299184004947</v>
       </c>
       <c r="E25">
-        <v>1.436080898992177</v>
+        <v>1.481723606674385</v>
       </c>
       <c r="F25">
         <v>0.9433471087059745</v>
@@ -9291,7 +9309,7 @@
         <v>0.8093364061548578</v>
       </c>
       <c r="I25">
-        <v>1.562608501833805</v>
+        <v>1.601328039195548</v>
       </c>
       <c r="J25">
         <v>1.123122797948854</v>
@@ -9309,7 +9327,7 @@
         <v>0.3967361961034241</v>
       </c>
       <c r="O25">
-        <v>0.8760535414176084</v>
+        <v>0.8847237651736796</v>
       </c>
       <c r="P25">
         <v>43</v>
@@ -9321,7 +9339,7 @@
         <v>31</v>
       </c>
       <c r="S25">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T25">
         <v>38</v>
@@ -9333,7 +9351,7 @@
         <v>30</v>
       </c>
       <c r="W25">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X25">
         <v>38</v>
@@ -9361,7 +9379,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.7012911626834096</v>
+        <v>0.7165656667433741</v>
       </c>
       <c r="C26">
         <v>1.330634043614174</v>
@@ -9370,7 +9388,7 @@
         <v>0.4036881503501098</v>
       </c>
       <c r="E26">
-        <v>0.9022837077654113</v>
+        <v>0.9309608328137686</v>
       </c>
       <c r="F26">
         <v>0.7270680665378959</v>
@@ -9382,7 +9400,7 @@
         <v>0.6274953054470301</v>
       </c>
       <c r="I26">
-        <v>1.065825581467118</v>
+        <v>1.09223544252591</v>
       </c>
       <c r="J26">
         <v>0.7777690204395585</v>
@@ -9400,7 +9418,7 @@
         <v>0.8838371688299902</v>
       </c>
       <c r="O26">
-        <v>0.7205004491236896</v>
+        <v>0.7259128714442368</v>
       </c>
       <c r="P26">
         <v>9</v>
@@ -9412,7 +9430,7 @@
         <v>14</v>
       </c>
       <c r="S26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T26">
         <v>32</v>
@@ -9442,7 +9460,7 @@
         <v>31</v>
       </c>
       <c r="AC26">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -9452,7 +9470,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.163514246288838</v>
+        <v>1.188856221240815</v>
       </c>
       <c r="C27">
         <v>1.013313270719777</v>
@@ -9461,7 +9479,7 @@
         <v>0.9620079293530099</v>
       </c>
       <c r="E27">
-        <v>1.099186758154736</v>
+        <v>1.134122018365926</v>
       </c>
       <c r="F27">
         <v>0.4682188669586645</v>
@@ -9473,7 +9491,7 @@
         <v>0.8238100361789056</v>
       </c>
       <c r="I27">
-        <v>1.505984350641695</v>
+        <v>1.543300810434689</v>
       </c>
       <c r="J27">
         <v>0.3994760157196676</v>
@@ -9491,7 +9509,7 @@
         <v>0.7603879886187158</v>
       </c>
       <c r="O27">
-        <v>0.8857253160274602</v>
+        <v>0.8932325233317802</v>
       </c>
       <c r="P27">
         <v>40</v>
@@ -9503,7 +9521,7 @@
         <v>29</v>
       </c>
       <c r="S27">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="T27">
         <v>17</v>
@@ -9515,7 +9533,7 @@
         <v>31</v>
       </c>
       <c r="W27">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X27">
         <v>14</v>
@@ -9533,7 +9551,7 @@
         <v>28</v>
       </c>
       <c r="AC27">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -9543,7 +9561,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9153726677709252</v>
+        <v>0.9353099837877813</v>
       </c>
       <c r="C28">
         <v>1.175230796870274</v>
@@ -9552,7 +9570,7 @@
         <v>0.7593405197421154</v>
       </c>
       <c r="E28">
-        <v>1.00636758042094</v>
+        <v>1.038352784963554</v>
       </c>
       <c r="F28">
         <v>0.5277727777711805</v>
@@ -9564,7 +9582,7 @@
         <v>2.006390010233103</v>
       </c>
       <c r="I28">
-        <v>0.8183571247844159</v>
+        <v>0.838635018595408</v>
       </c>
       <c r="J28">
         <v>0.2758963970711671</v>
@@ -9582,7 +9600,7 @@
         <v>0.5902752638181615</v>
       </c>
       <c r="O28">
-        <v>0.8717637445541385</v>
+        <v>0.8773176225826356</v>
       </c>
       <c r="P28">
         <v>23</v>
@@ -9594,7 +9612,7 @@
         <v>25</v>
       </c>
       <c r="S28">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T28">
         <v>23</v>
@@ -9634,7 +9652,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.00310562737891</v>
+        <v>1.024953815112154</v>
       </c>
       <c r="C29">
         <v>0.1700183134689107</v>
@@ -9643,7 +9661,7 @@
         <v>0.1528485071031518</v>
       </c>
       <c r="E29">
-        <v>1.156512993917818</v>
+        <v>1.19327024383954</v>
       </c>
       <c r="F29">
         <v>0.1394497076498046</v>
@@ -9655,7 +9673,7 @@
         <v>0.3610855846320352</v>
       </c>
       <c r="I29">
-        <v>1.231339933039217</v>
+        <v>1.26185103833934</v>
       </c>
       <c r="J29">
         <v>0.3617000084286194</v>
@@ -9673,7 +9691,7 @@
         <v>1.133233195507545</v>
       </c>
       <c r="O29">
-        <v>0.9022038253926883</v>
+        <v>0.9090589440815413</v>
       </c>
       <c r="P29">
         <v>33</v>
@@ -9685,7 +9703,7 @@
         <v>2</v>
       </c>
       <c r="S29">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -9725,7 +9743,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.8262989289772738</v>
+        <v>0.8442961703757161</v>
       </c>
       <c r="C30">
         <v>1.117261212209998</v>
@@ -9734,7 +9752,7 @@
         <v>0.2780565329131561</v>
       </c>
       <c r="E30">
-        <v>0.7810396514221293</v>
+        <v>0.8058632978636996</v>
       </c>
       <c r="F30">
         <v>0.07054786564547889</v>
@@ -9746,7 +9764,7 @@
         <v>0.3493831510969829</v>
       </c>
       <c r="I30">
-        <v>0.7076147166818574</v>
+        <v>0.7251485483665879</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -9764,7 +9782,7 @@
         <v>0.5881648038534175</v>
       </c>
       <c r="O30">
-        <v>0.6968975012445736</v>
+        <v>0.7015401719772462</v>
       </c>
       <c r="P30">
         <v>16</v>
@@ -9806,7 +9824,7 @@
         <v>19</v>
       </c>
       <c r="AC30">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -9816,7 +9834,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.6548248711751378</v>
+        <v>0.6690873140598569</v>
       </c>
       <c r="C31">
         <v>0.8929987573129358</v>
@@ -9825,7 +9843,7 @@
         <v>1.475209164352687</v>
       </c>
       <c r="E31">
-        <v>1.526590353605009</v>
+        <v>1.57510970743039</v>
       </c>
       <c r="F31">
         <v>0.6071251522102397</v>
@@ -9837,7 +9855,7 @@
         <v>1.23023411619943</v>
       </c>
       <c r="I31">
-        <v>0.7292051952075838</v>
+        <v>0.7472740126798316</v>
       </c>
       <c r="J31">
         <v>1.159920542229745</v>
@@ -9855,7 +9873,7 @@
         <v>1.739538513521424</v>
       </c>
       <c r="O31">
-        <v>1.221984365872963</v>
+        <v>1.22820364388699</v>
       </c>
       <c r="P31">
         <v>5</v>
@@ -9867,7 +9885,7 @@
         <v>34</v>
       </c>
       <c r="S31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T31">
         <v>26</v>
@@ -9897,7 +9915,7 @@
         <v>44</v>
       </c>
       <c r="AC31">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
@@ -9907,7 +9925,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.9060584231035613</v>
+        <v>0.9257928697908755</v>
       </c>
       <c r="C32">
         <v>0.6706945071743736</v>
@@ -9916,7 +9934,7 @@
         <v>1.546548735380322</v>
       </c>
       <c r="E32">
-        <v>1.408554848854871</v>
+        <v>1.45332270090677</v>
       </c>
       <c r="F32">
         <v>2.147443270229993</v>
@@ -9928,7 +9946,7 @@
         <v>1.129740539524886</v>
       </c>
       <c r="I32">
-        <v>1.445592623220356</v>
+        <v>1.481412649489863</v>
       </c>
       <c r="J32">
         <v>1.324183329369569</v>
@@ -9946,7 +9964,7 @@
         <v>0.7501223319957364</v>
       </c>
       <c r="O32">
-        <v>1.139168707494538</v>
+        <v>1.146885809418285</v>
       </c>
       <c r="P32">
         <v>20</v>
@@ -9958,7 +9976,7 @@
         <v>35</v>
       </c>
       <c r="S32">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T32">
         <v>44</v>
@@ -9970,7 +9988,7 @@
         <v>40</v>
       </c>
       <c r="W32">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X32">
         <v>41</v>
@@ -9998,7 +10016,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.8244322300749829</v>
+        <v>0.842388813753096</v>
       </c>
       <c r="C33">
         <v>1.402498498167605</v>
@@ -10007,7 +10025,7 @@
         <v>0.9262800385420014</v>
       </c>
       <c r="E33">
-        <v>0.4911681201793336</v>
+        <v>0.5067788305145926</v>
       </c>
       <c r="F33">
         <v>0.7791547734297884</v>
@@ -10019,7 +10037,7 @@
         <v>1.867981184888021</v>
       </c>
       <c r="I33">
-        <v>0.7317859393067448</v>
+        <v>0.7499187044776333</v>
       </c>
       <c r="J33">
         <v>2.200459451075125</v>
@@ -10037,7 +10055,7 @@
         <v>2.445766596452321</v>
       </c>
       <c r="O33">
-        <v>1.385250798279797</v>
+        <v>1.389227725909355</v>
       </c>
       <c r="P33">
         <v>15</v>
@@ -10089,7 +10107,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.98630745697769</v>
+        <v>1.007789771396616</v>
       </c>
       <c r="C34">
         <v>1.004718104899085</v>
@@ -10098,7 +10116,7 @@
         <v>0.5186220694597287</v>
       </c>
       <c r="E34">
-        <v>1.022288788123899</v>
+        <v>1.054780013622326</v>
       </c>
       <c r="F34">
         <v>0.514184530817918</v>
@@ -10110,7 +10128,7 @@
         <v>0.3940616950635396</v>
       </c>
       <c r="I34">
-        <v>0.9283560327768183</v>
+        <v>0.9513595656860007</v>
       </c>
       <c r="J34">
         <v>0.56260482586623</v>
@@ -10128,7 +10146,7 @@
         <v>0.4109581444227013</v>
       </c>
       <c r="O34">
-        <v>0.6565461216359185</v>
+        <v>0.6624674349302674</v>
       </c>
       <c r="P34">
         <v>30</v>
@@ -10140,7 +10158,7 @@
         <v>18</v>
       </c>
       <c r="S34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T34">
         <v>22</v>
@@ -10170,7 +10188,7 @@
         <v>12</v>
       </c>
       <c r="AC34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -10180,7 +10198,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.7496294294366646</v>
+        <v>0.7659567673138257</v>
       </c>
       <c r="C35">
         <v>1.631977687686749</v>
@@ -10189,7 +10207,7 @@
         <v>0.5869755332055396</v>
       </c>
       <c r="E35">
-        <v>0.7731956434389442</v>
+        <v>0.7977699851486677</v>
       </c>
       <c r="F35">
         <v>0.2326936116535781</v>
@@ -10201,7 +10219,7 @@
         <v>0.5712927097415086</v>
       </c>
       <c r="I35">
-        <v>0.3438802859526671</v>
+        <v>0.3524012210200789</v>
       </c>
       <c r="J35">
         <v>0.06604170553614229</v>
@@ -10219,7 +10237,7 @@
         <v>0.7509879344493596</v>
       </c>
       <c r="O35">
-        <v>0.6050064421643518</v>
+        <v>0.6088081817531438</v>
       </c>
       <c r="P35">
         <v>11</v>
@@ -10271,7 +10289,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.9296536275909441</v>
+        <v>0.9499019907025851</v>
       </c>
       <c r="C36">
         <v>0.7048404252615226</v>
@@ -10280,7 +10298,7 @@
         <v>0.4390426452245062</v>
       </c>
       <c r="E36">
-        <v>0.5813132049875491</v>
+        <v>0.5997889807643001</v>
       </c>
       <c r="F36">
         <v>0.4859053617727038</v>
@@ -10292,7 +10310,7 @@
         <v>0.9805053347674334</v>
       </c>
       <c r="I36">
-        <v>0.7163251931921798</v>
+        <v>0.7340748598863092</v>
       </c>
       <c r="J36">
         <v>0.7307101165483832</v>
@@ -10310,7 +10328,7 @@
         <v>0.4680229830217069</v>
       </c>
       <c r="O36">
-        <v>0.6384648409605833</v>
+        <v>0.6428089798515465</v>
       </c>
       <c r="P36">
         <v>26</v>
@@ -10362,7 +10380,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.30580864346613</v>
+        <v>1.334249868006648</v>
       </c>
       <c r="C37">
         <v>1.144557766631165</v>
@@ -10371,7 +10389,7 @@
         <v>2.080421926662737</v>
       </c>
       <c r="E37">
-        <v>0.8318615128518986</v>
+        <v>0.8583004216138107</v>
       </c>
       <c r="F37">
         <v>0.8679415792230573</v>
@@ -10383,7 +10401,7 @@
         <v>0.7894518983352597</v>
       </c>
       <c r="I37">
-        <v>1.117031646907113</v>
+        <v>1.144710331962207</v>
       </c>
       <c r="J37">
         <v>1.103159273498292</v>
@@ -10401,7 +10419,7 @@
         <v>1.402053986637626</v>
       </c>
       <c r="O37">
-        <v>1.260056423587073</v>
+        <v>1.266407101922267</v>
       </c>
       <c r="P37">
         <v>44</v>
@@ -10453,7 +10471,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.12166667189448</v>
+        <v>1.146097183849346</v>
       </c>
       <c r="C38">
         <v>0.6857345600490986</v>
@@ -10462,7 +10480,7 @@
         <v>0.3936379736038624</v>
       </c>
       <c r="E38">
-        <v>1.454427717839401</v>
+        <v>1.500653539251574</v>
       </c>
       <c r="F38">
         <v>0.2442738548810911</v>
@@ -10474,7 +10492,7 @@
         <v>0.7452610877930345</v>
       </c>
       <c r="I38">
-        <v>1.083288654589849</v>
+        <v>1.110131229352319</v>
       </c>
       <c r="J38">
         <v>0.5571415591091499</v>
@@ -10492,7 +10510,7 @@
         <v>1.285619247835468</v>
       </c>
       <c r="O38">
-        <v>0.9091485220380914</v>
+        <v>0.9166484380480536</v>
       </c>
       <c r="P38">
         <v>38</v>
@@ -10504,7 +10522,7 @@
         <v>13</v>
       </c>
       <c r="S38">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T38">
         <v>12</v>
@@ -10534,7 +10552,7 @@
         <v>38</v>
       </c>
       <c r="AC38">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
@@ -10544,7 +10562,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.10673535631864</v>
+        <v>1.130840656075606</v>
       </c>
       <c r="C39">
         <v>1.871214547826957</v>
@@ -10553,7 +10571,7 @@
         <v>1.302544402056047</v>
       </c>
       <c r="E39">
-        <v>0.5050376456501077</v>
+        <v>0.5210891686841483</v>
       </c>
       <c r="F39">
         <v>0.9623708124269743</v>
@@ -10565,7 +10583,7 @@
         <v>1.039929629360226</v>
       </c>
       <c r="I39">
-        <v>1.061792018844983</v>
+        <v>1.088101933129862</v>
       </c>
       <c r="J39">
         <v>1.404796235942467</v>
@@ -10583,7 +10601,7 @@
         <v>1.153196537384685</v>
       </c>
       <c r="O39">
-        <v>1.050091542765911</v>
+        <v>1.055204368694825</v>
       </c>
       <c r="P39">
         <v>35</v>
@@ -10635,7 +10653,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.6412419700794157</v>
+        <v>0.6552085699691385</v>
       </c>
       <c r="C40">
         <v>2.259862939366645</v>
@@ -10644,7 +10662,7 @@
         <v>4.855515006617974</v>
       </c>
       <c r="E40">
-        <v>0.4975937089671547</v>
+        <v>0.5134086426654111</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -10656,7 +10674,7 @@
         <v>1.979573323621126</v>
       </c>
       <c r="I40">
-        <v>0.524496507859315</v>
+        <v>0.5374928931396524</v>
       </c>
       <c r="J40">
         <v>0.1608284295981063</v>
@@ -10674,7 +10692,7 @@
         <v>0.3159952712315088</v>
       </c>
       <c r="O40">
-        <v>1.093759558498969</v>
+        <v>1.097050167642686</v>
       </c>
       <c r="P40">
         <v>4</v>
@@ -10726,7 +10744,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>1.319554659544971</v>
+        <v>1.348295279813793</v>
       </c>
       <c r="C41">
         <v>0.9181810055459642</v>
@@ -10735,7 +10753,7 @@
         <v>0.5750700015968063</v>
       </c>
       <c r="E41">
-        <v>1.505587976077368</v>
+        <v>1.553439815016368</v>
       </c>
       <c r="F41">
         <v>0.5668821938130079</v>
@@ -10747,7 +10765,7 @@
         <v>0.212530599588442</v>
       </c>
       <c r="I41">
-        <v>1.364233151056419</v>
+        <v>1.398037188600351</v>
       </c>
       <c r="J41">
         <v>0.5975888047625311</v>
@@ -10765,7 +10783,7 @@
         <v>0.009339233094551768</v>
       </c>
       <c r="O41">
-        <v>0.6572724273516196</v>
+        <v>0.6657644655632929</v>
       </c>
       <c r="P41">
         <v>45</v>
@@ -10777,7 +10795,7 @@
         <v>20</v>
       </c>
       <c r="S41">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T41">
         <v>24</v>
@@ -10789,7 +10807,7 @@
         <v>5</v>
       </c>
       <c r="W41">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X41">
         <v>21</v>
@@ -10807,7 +10825,7 @@
         <v>1</v>
       </c>
       <c r="AC41">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -10817,7 +10835,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.396585599987767</v>
+        <v>1.427003996157877</v>
       </c>
       <c r="C42">
         <v>2.432367276005801</v>
@@ -10826,7 +10844,7 @@
         <v>0.7558649544877212</v>
       </c>
       <c r="E42">
-        <v>0.9344638839653246</v>
+        <v>0.9641637859174659</v>
       </c>
       <c r="F42">
         <v>0.151481846373294</v>
@@ -10838,7 +10856,7 @@
         <v>0.5646491008120046</v>
       </c>
       <c r="I42">
-        <v>0.5409509730267414</v>
+        <v>0.5543550799328539</v>
       </c>
       <c r="J42">
         <v>0.3773530165900005</v>
@@ -10856,7 +10874,7 @@
         <v>0.8440146386040174</v>
       </c>
       <c r="O42">
-        <v>0.9096024965859165</v>
+        <v>0.9152580662034829</v>
       </c>
       <c r="P42">
         <v>47</v>
@@ -10868,7 +10886,7 @@
         <v>24</v>
       </c>
       <c r="S42">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T42">
         <v>7</v>
@@ -10898,7 +10916,7 @@
         <v>29</v>
       </c>
       <c r="AC42">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
@@ -10907,12 +10925,18 @@
           <t>Tennessee</t>
         </is>
       </c>
+      <c r="B43">
+        <v>1.431936547938054</v>
+      </c>
       <c r="C43">
         <v>0.655224861978378</v>
       </c>
       <c r="D43">
         <v>1.221660541659172</v>
       </c>
+      <c r="E43">
+        <v>0.8651027249376209</v>
+      </c>
       <c r="F43">
         <v>0.3433372194317119</v>
       </c>
@@ -10922,6 +10946,9 @@
       <c r="H43">
         <v>0.2747156427087664</v>
       </c>
+      <c r="I43">
+        <v>1.38546975240875</v>
+      </c>
       <c r="J43">
         <v>0.4041546555524553</v>
       </c>
@@ -10938,7 +10965,10 @@
         <v>0.03587177561103919</v>
       </c>
       <c r="O43">
-        <v>0.6453484324967789</v>
+        <v>0.7796917961732471</v>
+      </c>
+      <c r="P43">
+        <v>48</v>
       </c>
       <c r="Q43">
         <v>11</v>
@@ -10946,6 +10976,9 @@
       <c r="R43">
         <v>32</v>
       </c>
+      <c r="S43">
+        <v>22</v>
+      </c>
       <c r="T43">
         <v>13</v>
       </c>
@@ -10955,6 +10988,9 @@
       <c r="V43">
         <v>9</v>
       </c>
+      <c r="W43">
+        <v>46</v>
+      </c>
       <c r="X43">
         <v>16</v>
       </c>
@@ -10971,7 +11007,7 @@
         <v>2</v>
       </c>
       <c r="AC43">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
@@ -10981,7 +11017,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.188612903083</v>
+        <v>1.214501540470641</v>
       </c>
       <c r="C44">
         <v>0.1821698820855988</v>
@@ -10990,7 +11026,7 @@
         <v>0.4554971984010375</v>
       </c>
       <c r="E44">
-        <v>1.162397589370366</v>
+        <v>1.199341868358666</v>
       </c>
       <c r="F44">
         <v>0.4824333801844599</v>
@@ -11002,7 +11038,7 @@
         <v>0.9880749601118354</v>
       </c>
       <c r="I44">
-        <v>1.075943617286769</v>
+        <v>1.102604190961989</v>
       </c>
       <c r="J44">
         <v>1.00257693381607</v>
@@ -11020,7 +11056,7 @@
         <v>1.366707406314812</v>
       </c>
       <c r="O44">
-        <v>0.9380161414093297</v>
+        <v>0.9449002560286496</v>
       </c>
       <c r="P44">
         <v>41</v>
@@ -11032,7 +11068,7 @@
         <v>16</v>
       </c>
       <c r="S44">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T44">
         <v>19</v>
@@ -11062,7 +11098,7 @@
         <v>39</v>
       </c>
       <c r="AC44">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
@@ -11072,7 +11108,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.5581166618578144</v>
+        <v>0.5702727471917024</v>
       </c>
       <c r="C45">
         <v>0.4330003738317756</v>
@@ -11081,7 +11117,7 @@
         <v>0.2614532931323879</v>
       </c>
       <c r="E45">
-        <v>1.025718291049169</v>
+        <v>1.05831851583839</v>
       </c>
       <c r="F45">
         <v>0.2288623133913589</v>
@@ -11093,7 +11129,7 @@
         <v>0.2127317224393538</v>
       </c>
       <c r="I45">
-        <v>0.5748306489580042</v>
+        <v>0.589074253010385</v>
       </c>
       <c r="J45">
         <v>0.5452004439862309</v>
@@ -11111,7 +11147,7 @@
         <v>1.028794854312139</v>
       </c>
       <c r="O45">
-        <v>0.6292430340114411</v>
+        <v>0.6337814889480172</v>
       </c>
       <c r="P45">
         <v>3</v>
@@ -11123,7 +11159,7 @@
         <v>7</v>
       </c>
       <c r="S45">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T45">
         <v>9</v>
@@ -11163,7 +11199,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.6868394189876488</v>
+        <v>0.7017991561868563</v>
       </c>
       <c r="C46">
         <v>0.4312264226300551</v>
@@ -11172,7 +11208,7 @@
         <v>1.795922227469368</v>
       </c>
       <c r="E46">
-        <v>0.4699085794972739</v>
+        <v>0.4848436015746567</v>
       </c>
       <c r="F46">
         <v>0.4243113561860449</v>
@@ -11184,7 +11220,7 @@
         <v>0.7270227052228045</v>
       </c>
       <c r="I46">
-        <v>0.5923456769499468</v>
+        <v>0.6070232820844478</v>
       </c>
       <c r="J46">
         <v>0.1670948929463442</v>
@@ -11202,7 +11238,7 @@
         <v>2.019732927744569</v>
       </c>
       <c r="O46">
-        <v>1.166909373289312</v>
+        <v>1.17033801670555</v>
       </c>
       <c r="P46">
         <v>8</v>
@@ -11254,7 +11290,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.9194554568706659</v>
+        <v>0.9394816982611732</v>
       </c>
       <c r="C47">
         <v>0.5033375655237308</v>
@@ -11263,7 +11299,7 @@
         <v>0.5006373644797254</v>
       </c>
       <c r="E47">
-        <v>1.089093996069861</v>
+        <v>1.12370847979146</v>
       </c>
       <c r="F47">
         <v>0.4907540787728799</v>
@@ -11275,7 +11311,7 @@
         <v>0.4720771532035531</v>
       </c>
       <c r="I47">
-        <v>0.6977012577146793</v>
+        <v>0.7149894459484665</v>
       </c>
       <c r="J47">
         <v>0.9460900051729214</v>
@@ -11293,7 +11329,7 @@
         <v>0.466758744579316</v>
       </c>
       <c r="O47">
-        <v>0.6761498688427943</v>
+        <v>0.6816828621770938</v>
       </c>
       <c r="P47">
         <v>25</v>
@@ -11305,7 +11341,7 @@
         <v>17</v>
       </c>
       <c r="S47">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T47">
         <v>21</v>
@@ -11335,7 +11371,7 @@
         <v>14</v>
       </c>
       <c r="AC47">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -11345,7 +11381,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.002455299314826</v>
+        <v>1.024289322548097</v>
       </c>
       <c r="C48">
         <v>0.8106817877562473</v>
@@ -11354,7 +11390,7 @@
         <v>1.140330802003307</v>
       </c>
       <c r="E48">
-        <v>0.9154915662554906</v>
+        <v>0.9445884743568733</v>
       </c>
       <c r="F48">
         <v>2.904435073385776</v>
@@ -11366,7 +11402,7 @@
         <v>1.505843443730358</v>
       </c>
       <c r="I48">
-        <v>1.058753472719543</v>
+        <v>1.084988095528603</v>
       </c>
       <c r="J48">
         <v>0.975060570841201</v>
@@ -11384,7 +11420,7 @@
         <v>4.884562462193406</v>
       </c>
       <c r="O48">
-        <v>1.805976711620305</v>
+        <v>1.811912523477513</v>
       </c>
       <c r="P48">
         <v>31</v>
@@ -11396,7 +11432,7 @@
         <v>30</v>
       </c>
       <c r="S48">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T48">
         <v>46</v>
@@ -11436,7 +11472,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.434517247736388</v>
+        <v>1.465761815885224</v>
       </c>
       <c r="C49">
         <v>2.772351675969673</v>
@@ -11445,7 +11481,7 @@
         <v>1.891333552300565</v>
       </c>
       <c r="E49">
-        <v>0.6185189898333322</v>
+        <v>0.6381772705532205</v>
       </c>
       <c r="F49">
         <v>0.9124974859722969</v>
@@ -11457,7 +11493,7 @@
         <v>0.4646711270866573</v>
       </c>
       <c r="I49">
-        <v>1.289797039886346</v>
+        <v>1.32175664116609</v>
       </c>
       <c r="J49">
         <v>0.8304050688849586</v>
@@ -11475,10 +11511,10 @@
         <v>0.4010302277091328</v>
       </c>
       <c r="O49">
-        <v>0.9745036517166947</v>
+        <v>0.9808776863434999</v>
       </c>
       <c r="P49">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q49">
         <v>49</v>
@@ -11527,7 +11563,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.8116526760613654</v>
+        <v>0.8293309140821361</v>
       </c>
       <c r="C50">
         <v>0.9696169367902057</v>
@@ -11536,7 +11572,7 @@
         <v>1.764533859218351</v>
       </c>
       <c r="E50">
-        <v>0.4262779692535499</v>
+        <v>0.4398262872874848</v>
       </c>
       <c r="F50">
         <v>0.6902941379954214</v>
@@ -11548,7 +11584,7 @@
         <v>1.500438543700507</v>
       </c>
       <c r="I50">
-        <v>0.66666884283464</v>
+        <v>0.6831880855865854</v>
       </c>
       <c r="J50">
         <v>0.7361909956654326</v>
@@ -11566,7 +11602,7 @@
         <v>2.235424562700156</v>
       </c>
       <c r="O50">
-        <v>0.9788796079034326</v>
+        <v>0.9825523616577905</v>
       </c>
       <c r="P50">
         <v>13</v>
@@ -11618,7 +11654,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8738354678900174</v>
+        <v>0.8928680810359678</v>
       </c>
       <c r="C51">
         <v>0.9672773404832817</v>
@@ -11627,7 +11663,7 @@
         <v>0.1486481678661591</v>
       </c>
       <c r="E51">
-        <v>0.8250067906267997</v>
+        <v>0.8512278369528403</v>
       </c>
       <c r="F51">
         <v>0.5828327766094176</v>
@@ -11639,7 +11675,7 @@
         <v>0.5766022673643969</v>
       </c>
       <c r="I51">
-        <v>1.094795888567732</v>
+        <v>1.121923598586675</v>
       </c>
       <c r="J51">
         <v>1.565845671706672</v>
@@ -11657,7 +11693,7 @@
         <v>0.4976698025801061</v>
       </c>
       <c r="O51">
-        <v>0.7427588431377932</v>
+        <v>0.7483266407909419</v>
       </c>
       <c r="P51">
         <v>17</v>
@@ -11699,7 +11735,7 @@
         <v>16</v>
       </c>
       <c r="AC51">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/AHR 30th/output/AHR_data 30th.xlsx
+++ b/AHR 30th/output/AHR_data 30th.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet name="AHR Data" sheetId="1" r:id="rId1"/>
     <sheet name="Scores &amp; Rankings" sheetId="2" r:id="rId2"/>
-    <sheet name="Disbursement Data" sheetId="3" r:id="rId3"/>
+    <sheet name="All Rankings" sheetId="3" r:id="rId3"/>
+    <sheet name="Disbursement Data" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -11745,6 +11746,2850 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>overall_rank</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>capital_disbursement_perlm_rank</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_disbursement_perlm_rank</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>admin_disbursement_perlm_rank</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>other_disbursement_perlm_rank</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_poor_percent_rank</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_poor_percent_rank</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_poor_percent_rank</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_poor_percent_rank</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>state_avg_congestion_hours_rank</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>poor_bridges_percent_rank</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rural_fatalities_per_100m_VMT_rank</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>urban_fatalities_per_100m_VMT_rank</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>other_fatalities_per_100m_VMT_rank</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>state_avg_congestion_hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2024</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>34</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="H2">
+        <v>30</v>
+      </c>
+      <c r="I2">
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>11</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>12</v>
+      </c>
+      <c r="M2">
+        <v>9</v>
+      </c>
+      <c r="N2">
+        <v>42</v>
+      </c>
+      <c r="O2">
+        <v>36</v>
+      </c>
+      <c r="P2">
+        <v>29</v>
+      </c>
+      <c r="Q2">
+        <v>14.92497349567402</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2024</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>48</v>
+      </c>
+      <c r="E3">
+        <v>32</v>
+      </c>
+      <c r="F3">
+        <v>26</v>
+      </c>
+      <c r="G3">
+        <v>23</v>
+      </c>
+      <c r="H3">
+        <v>49</v>
+      </c>
+      <c r="I3">
+        <v>11</v>
+      </c>
+      <c r="J3">
+        <v>50</v>
+      </c>
+      <c r="K3">
+        <v>15</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>36</v>
+      </c>
+      <c r="N3">
+        <v>49</v>
+      </c>
+      <c r="O3">
+        <v>45</v>
+      </c>
+      <c r="P3">
+        <v>7</v>
+      </c>
+      <c r="Q3">
+        <v>13.81548264455274</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2024</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>42</v>
+      </c>
+      <c r="D4">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>46</v>
+      </c>
+      <c r="G4">
+        <v>43</v>
+      </c>
+      <c r="H4">
+        <v>42</v>
+      </c>
+      <c r="I4">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>46</v>
+      </c>
+      <c r="K4">
+        <v>21</v>
+      </c>
+      <c r="L4">
+        <v>35</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4">
+        <v>40</v>
+      </c>
+      <c r="O4">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>50</v>
+      </c>
+      <c r="Q4">
+        <v>32.30385952393645</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2024</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>24</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>9</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>36</v>
+      </c>
+      <c r="I5">
+        <v>33</v>
+      </c>
+      <c r="J5">
+        <v>22</v>
+      </c>
+      <c r="K5">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>17</v>
+      </c>
+      <c r="M5">
+        <v>22</v>
+      </c>
+      <c r="N5">
+        <v>48</v>
+      </c>
+      <c r="O5">
+        <v>26</v>
+      </c>
+      <c r="P5">
+        <v>42</v>
+      </c>
+      <c r="Q5">
+        <v>16.89708425743395</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2024</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+      <c r="F6">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>41</v>
+      </c>
+      <c r="H6">
+        <v>45</v>
+      </c>
+      <c r="I6">
+        <v>47</v>
+      </c>
+      <c r="J6">
+        <v>41</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6">
+        <v>46</v>
+      </c>
+      <c r="M6">
+        <v>24</v>
+      </c>
+      <c r="N6">
+        <v>31</v>
+      </c>
+      <c r="O6">
+        <v>23</v>
+      </c>
+      <c r="P6">
+        <v>39</v>
+      </c>
+      <c r="Q6">
+        <v>49.57699007444302</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2024</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>45</v>
+      </c>
+      <c r="D7">
+        <v>35</v>
+      </c>
+      <c r="E7">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+      <c r="H7">
+        <v>48</v>
+      </c>
+      <c r="I7">
+        <v>45</v>
+      </c>
+      <c r="J7">
+        <v>37</v>
+      </c>
+      <c r="K7">
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>18</v>
+      </c>
+      <c r="N7">
+        <v>36</v>
+      </c>
+      <c r="O7">
+        <v>41</v>
+      </c>
+      <c r="P7">
+        <v>18</v>
+      </c>
+      <c r="Q7">
+        <v>32.86214588182396</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>2024</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>19</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+      <c r="F8">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>12</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+      <c r="K8">
+        <v>23</v>
+      </c>
+      <c r="L8">
+        <v>24</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8">
+        <v>19</v>
+      </c>
+      <c r="P8">
+        <v>32</v>
+      </c>
+      <c r="Q8">
+        <v>22.35631765319591</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>2024</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>40</v>
+      </c>
+      <c r="J9">
+        <v>8</v>
+      </c>
+      <c r="K9">
+        <v>13</v>
+      </c>
+      <c r="L9">
+        <v>49</v>
+      </c>
+      <c r="M9">
+        <v>4</v>
+      </c>
+      <c r="N9">
+        <v>18</v>
+      </c>
+      <c r="O9">
+        <v>27</v>
+      </c>
+      <c r="P9">
+        <v>37</v>
+      </c>
+      <c r="Q9">
+        <v>62.30051462520785</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>2024</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>38</v>
+      </c>
+      <c r="E10">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10">
+        <v>6</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10">
+        <v>40</v>
+      </c>
+      <c r="M10">
+        <v>6</v>
+      </c>
+      <c r="N10">
+        <v>41</v>
+      </c>
+      <c r="O10">
+        <v>39</v>
+      </c>
+      <c r="P10">
+        <v>14</v>
+      </c>
+      <c r="Q10">
+        <v>38.70093181597566</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>2024</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>4</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>22</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11">
+        <v>15</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <v>45</v>
+      </c>
+      <c r="M11">
+        <v>5</v>
+      </c>
+      <c r="N11">
+        <v>13</v>
+      </c>
+      <c r="O11">
+        <v>32</v>
+      </c>
+      <c r="P11">
+        <v>24</v>
+      </c>
+      <c r="Q11">
+        <v>49.30484682122379</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>2024</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>48</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>24</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <v>47</v>
+      </c>
+      <c r="I12">
+        <v>50</v>
+      </c>
+      <c r="J12">
+        <v>48</v>
+      </c>
+      <c r="K12">
+        <v>38</v>
+      </c>
+      <c r="L12">
+        <v>18</v>
+      </c>
+      <c r="M12">
+        <v>30</v>
+      </c>
+      <c r="N12">
+        <v>50</v>
+      </c>
+      <c r="O12">
+        <v>38</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>17.28295956677959</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>2024</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13">
+        <v>49</v>
+      </c>
+      <c r="E13">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>18</v>
+      </c>
+      <c r="G13">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>18</v>
+      </c>
+      <c r="I13">
+        <v>15</v>
+      </c>
+      <c r="J13">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>34</v>
+      </c>
+      <c r="L13">
+        <v>14</v>
+      </c>
+      <c r="M13">
+        <v>19</v>
+      </c>
+      <c r="N13">
+        <v>39</v>
+      </c>
+      <c r="O13">
+        <v>11</v>
+      </c>
+      <c r="P13">
+        <v>19</v>
+      </c>
+      <c r="Q13">
+        <v>16.16501222292439</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>2024</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>37</v>
+      </c>
+      <c r="D14">
+        <v>36</v>
+      </c>
+      <c r="E14">
+        <v>20</v>
+      </c>
+      <c r="F14">
+        <v>19</v>
+      </c>
+      <c r="G14">
+        <v>32</v>
+      </c>
+      <c r="H14">
+        <v>27</v>
+      </c>
+      <c r="I14">
+        <v>36</v>
+      </c>
+      <c r="J14">
+        <v>45</v>
+      </c>
+      <c r="K14">
+        <v>33</v>
+      </c>
+      <c r="L14">
+        <v>44</v>
+      </c>
+      <c r="M14">
+        <v>40</v>
+      </c>
+      <c r="N14">
+        <v>20</v>
+      </c>
+      <c r="O14">
+        <v>25</v>
+      </c>
+      <c r="P14">
+        <v>22</v>
+      </c>
+      <c r="Q14">
+        <v>47.6989037489919</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>2024</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>24</v>
+      </c>
+      <c r="D15">
+        <v>47</v>
+      </c>
+      <c r="E15">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>3</v>
+      </c>
+      <c r="H15">
+        <v>41</v>
+      </c>
+      <c r="I15">
+        <v>35</v>
+      </c>
+      <c r="J15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>7</v>
+      </c>
+      <c r="L15">
+        <v>30</v>
+      </c>
+      <c r="M15">
+        <v>20</v>
+      </c>
+      <c r="N15">
+        <v>26</v>
+      </c>
+      <c r="O15">
+        <v>16</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15">
+        <v>24.82505210305955</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>34</v>
+      </c>
+      <c r="D16">
+        <v>39</v>
+      </c>
+      <c r="E16">
+        <v>19</v>
+      </c>
+      <c r="F16">
+        <v>27</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>27</v>
+      </c>
+      <c r="J16">
+        <v>36</v>
+      </c>
+      <c r="K16">
+        <v>25</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>50</v>
+      </c>
+      <c r="N16">
+        <v>8</v>
+      </c>
+      <c r="O16">
+        <v>10</v>
+      </c>
+      <c r="P16">
+        <v>34</v>
+      </c>
+      <c r="Q16">
+        <v>11.13382852973375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>2024</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>44</v>
+      </c>
+      <c r="E17">
+        <v>18</v>
+      </c>
+      <c r="F17">
+        <v>36</v>
+      </c>
+      <c r="G17">
+        <v>49</v>
+      </c>
+      <c r="H17">
+        <v>11</v>
+      </c>
+      <c r="I17">
+        <v>20</v>
+      </c>
+      <c r="J17">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>17</v>
+      </c>
+      <c r="L17">
+        <v>3</v>
+      </c>
+      <c r="M17">
+        <v>21</v>
+      </c>
+      <c r="N17">
+        <v>17</v>
+      </c>
+      <c r="O17">
+        <v>13</v>
+      </c>
+      <c r="P17">
+        <v>21</v>
+      </c>
+      <c r="Q17">
+        <v>11.41799387956611</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>2024</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>14</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>24</v>
+      </c>
+      <c r="H18">
+        <v>14</v>
+      </c>
+      <c r="I18">
+        <v>34</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+      <c r="K18">
+        <v>8</v>
+      </c>
+      <c r="L18">
+        <v>28</v>
+      </c>
+      <c r="M18">
+        <v>33</v>
+      </c>
+      <c r="N18">
+        <v>24</v>
+      </c>
+      <c r="O18">
+        <v>24</v>
+      </c>
+      <c r="P18">
+        <v>46</v>
+      </c>
+      <c r="Q18">
+        <v>24.36734572931871</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>2024</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>17</v>
+      </c>
+      <c r="E19">
+        <v>31</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>9</v>
+      </c>
+      <c r="H19">
+        <v>43</v>
+      </c>
+      <c r="I19">
+        <v>49</v>
+      </c>
+      <c r="J19">
+        <v>47</v>
+      </c>
+      <c r="K19">
+        <v>42</v>
+      </c>
+      <c r="L19">
+        <v>29</v>
+      </c>
+      <c r="M19">
+        <v>44</v>
+      </c>
+      <c r="N19">
+        <v>23</v>
+      </c>
+      <c r="O19">
+        <v>42</v>
+      </c>
+      <c r="P19">
+        <v>36</v>
+      </c>
+      <c r="Q19">
+        <v>24.61807391399524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>2024</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>18</v>
+      </c>
+      <c r="D20">
+        <v>23</v>
+      </c>
+      <c r="E20">
+        <v>40</v>
+      </c>
+      <c r="F20">
+        <v>15</v>
+      </c>
+      <c r="G20">
+        <v>22</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20">
+        <v>42</v>
+      </c>
+      <c r="K20">
+        <v>28</v>
+      </c>
+      <c r="L20">
+        <v>8</v>
+      </c>
+      <c r="M20">
+        <v>47</v>
+      </c>
+      <c r="N20">
+        <v>29</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <v>28</v>
+      </c>
+      <c r="Q20">
+        <v>13.25679123785564</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>2024</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>36</v>
+      </c>
+      <c r="D21">
+        <v>37</v>
+      </c>
+      <c r="E21">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>33</v>
+      </c>
+      <c r="G21">
+        <v>42</v>
+      </c>
+      <c r="H21">
+        <v>28</v>
+      </c>
+      <c r="I21">
+        <v>44</v>
+      </c>
+      <c r="J21">
+        <v>28</v>
+      </c>
+      <c r="K21">
+        <v>43</v>
+      </c>
+      <c r="L21">
+        <v>43</v>
+      </c>
+      <c r="M21">
+        <v>14</v>
+      </c>
+      <c r="N21">
+        <v>7</v>
+      </c>
+      <c r="O21">
+        <v>28</v>
+      </c>
+      <c r="P21">
+        <v>12</v>
+      </c>
+      <c r="Q21">
+        <v>46.65161245663136</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>2024</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>23</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22">
+        <v>44</v>
+      </c>
+      <c r="F22">
+        <v>42</v>
+      </c>
+      <c r="G22">
+        <v>21</v>
+      </c>
+      <c r="H22">
+        <v>31</v>
+      </c>
+      <c r="I22">
+        <v>24</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>46</v>
+      </c>
+      <c r="L22">
+        <v>47</v>
+      </c>
+      <c r="M22">
+        <v>38</v>
+      </c>
+      <c r="N22">
+        <v>11</v>
+      </c>
+      <c r="O22">
+        <v>6</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>58.76944652718411</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>2024</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>19</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>13</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23">
+        <v>17</v>
+      </c>
+      <c r="H23">
+        <v>40</v>
+      </c>
+      <c r="I23">
+        <v>42</v>
+      </c>
+      <c r="J23">
+        <v>19</v>
+      </c>
+      <c r="K23">
+        <v>32</v>
+      </c>
+      <c r="L23">
+        <v>16</v>
+      </c>
+      <c r="M23">
+        <v>43</v>
+      </c>
+      <c r="N23">
+        <v>12</v>
+      </c>
+      <c r="O23">
+        <v>21</v>
+      </c>
+      <c r="P23">
+        <v>27</v>
+      </c>
+      <c r="Q23">
+        <v>16.82923588211923</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>2024</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>25</v>
+      </c>
+      <c r="E24">
+        <v>43</v>
+      </c>
+      <c r="F24">
+        <v>39</v>
+      </c>
+      <c r="G24">
+        <v>45</v>
+      </c>
+      <c r="H24">
+        <v>8</v>
+      </c>
+      <c r="I24">
+        <v>13</v>
+      </c>
+      <c r="J24">
+        <v>23</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24">
+        <v>26</v>
+      </c>
+      <c r="M24">
+        <v>12</v>
+      </c>
+      <c r="N24">
+        <v>15</v>
+      </c>
+      <c r="O24">
+        <v>2</v>
+      </c>
+      <c r="P24">
+        <v>6</v>
+      </c>
+      <c r="Q24">
+        <v>23.42269110231913</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>2024</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>22</v>
+      </c>
+      <c r="D25">
+        <v>16</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>5</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25">
+        <v>38</v>
+      </c>
+      <c r="I25">
+        <v>38</v>
+      </c>
+      <c r="J25">
+        <v>31</v>
+      </c>
+      <c r="K25">
+        <v>30</v>
+      </c>
+      <c r="L25">
+        <v>11</v>
+      </c>
+      <c r="M25">
+        <v>26</v>
+      </c>
+      <c r="N25">
+        <v>44</v>
+      </c>
+      <c r="O25">
+        <v>50</v>
+      </c>
+      <c r="P25">
+        <v>43</v>
+      </c>
+      <c r="Q25">
+        <v>14.25151837354446</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>2024</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>11</v>
+      </c>
+      <c r="F26">
+        <v>4</v>
+      </c>
+      <c r="G26">
+        <v>31</v>
+      </c>
+      <c r="H26">
+        <v>32</v>
+      </c>
+      <c r="I26">
+        <v>28</v>
+      </c>
+      <c r="J26">
+        <v>14</v>
+      </c>
+      <c r="K26">
+        <v>22</v>
+      </c>
+      <c r="L26">
+        <v>23</v>
+      </c>
+      <c r="M26">
+        <v>39</v>
+      </c>
+      <c r="N26">
+        <v>25</v>
+      </c>
+      <c r="O26">
+        <v>31</v>
+      </c>
+      <c r="P26">
+        <v>9</v>
+      </c>
+      <c r="Q26">
+        <v>22.01812732034156</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>2024</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>25</v>
+      </c>
+      <c r="D27">
+        <v>18</v>
+      </c>
+      <c r="E27">
+        <v>38</v>
+      </c>
+      <c r="F27">
+        <v>35</v>
+      </c>
+      <c r="G27">
+        <v>28</v>
+      </c>
+      <c r="H27">
+        <v>17</v>
+      </c>
+      <c r="I27">
+        <v>14</v>
+      </c>
+      <c r="J27">
+        <v>29</v>
+      </c>
+      <c r="K27">
+        <v>31</v>
+      </c>
+      <c r="L27">
+        <v>4</v>
+      </c>
+      <c r="M27">
+        <v>32</v>
+      </c>
+      <c r="N27">
+        <v>35</v>
+      </c>
+      <c r="O27">
+        <v>49</v>
+      </c>
+      <c r="P27">
+        <v>40</v>
+      </c>
+      <c r="Q27">
+        <v>11.46640944563405</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>2024</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>21</v>
+      </c>
+      <c r="D28">
+        <v>26</v>
+      </c>
+      <c r="E28">
+        <v>27</v>
+      </c>
+      <c r="F28">
+        <v>25</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28">
+        <v>23</v>
+      </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
+      <c r="J28">
+        <v>25</v>
+      </c>
+      <c r="K28">
+        <v>49</v>
+      </c>
+      <c r="L28">
+        <v>22</v>
+      </c>
+      <c r="M28">
+        <v>37</v>
+      </c>
+      <c r="N28">
+        <v>30</v>
+      </c>
+      <c r="O28">
+        <v>20</v>
+      </c>
+      <c r="P28">
+        <v>23</v>
+      </c>
+      <c r="Q28">
+        <v>19.50965191227439</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>2024</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>46</v>
+      </c>
+      <c r="E29">
+        <v>42</v>
+      </c>
+      <c r="F29">
+        <v>48</v>
+      </c>
+      <c r="G29">
+        <v>36</v>
+      </c>
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="I29">
+        <v>9</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>11</v>
+      </c>
+      <c r="L29">
+        <v>27</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>37</v>
+      </c>
+      <c r="O29">
+        <v>40</v>
+      </c>
+      <c r="P29">
+        <v>33</v>
+      </c>
+      <c r="Q29">
+        <v>23.52525588127664</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>2024</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>12</v>
+      </c>
+      <c r="D30">
+        <v>15</v>
+      </c>
+      <c r="E30">
+        <v>36</v>
+      </c>
+      <c r="F30">
+        <v>44</v>
+      </c>
+      <c r="G30">
+        <v>19</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="K30">
+        <v>10</v>
+      </c>
+      <c r="L30">
+        <v>31</v>
+      </c>
+      <c r="M30">
+        <v>34</v>
+      </c>
+      <c r="N30">
+        <v>16</v>
+      </c>
+      <c r="O30">
+        <v>14</v>
+      </c>
+      <c r="P30">
+        <v>16</v>
+      </c>
+      <c r="Q30">
+        <v>25.33281815602586</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>2024</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>41</v>
+      </c>
+      <c r="D31">
+        <v>45</v>
+      </c>
+      <c r="E31">
+        <v>33</v>
+      </c>
+      <c r="F31">
+        <v>31</v>
+      </c>
+      <c r="G31">
+        <v>44</v>
+      </c>
+      <c r="H31">
+        <v>26</v>
+      </c>
+      <c r="I31">
+        <v>39</v>
+      </c>
+      <c r="J31">
+        <v>34</v>
+      </c>
+      <c r="K31">
+        <v>41</v>
+      </c>
+      <c r="L31">
+        <v>50</v>
+      </c>
+      <c r="M31">
+        <v>25</v>
+      </c>
+      <c r="N31">
+        <v>47</v>
+      </c>
+      <c r="O31">
+        <v>17</v>
+      </c>
+      <c r="P31">
+        <v>5</v>
+      </c>
+      <c r="Q31">
+        <v>86.89001435083415</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>2024</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>39</v>
+      </c>
+      <c r="D32">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>45</v>
+      </c>
+      <c r="G32">
+        <v>26</v>
+      </c>
+      <c r="H32">
+        <v>44</v>
+      </c>
+      <c r="I32">
+        <v>41</v>
+      </c>
+      <c r="J32">
+        <v>35</v>
+      </c>
+      <c r="K32">
+        <v>40</v>
+      </c>
+      <c r="L32">
+        <v>13</v>
+      </c>
+      <c r="M32">
+        <v>13</v>
+      </c>
+      <c r="N32">
+        <v>43</v>
+      </c>
+      <c r="O32">
+        <v>48</v>
+      </c>
+      <c r="P32">
+        <v>20</v>
+      </c>
+      <c r="Q32">
+        <v>15.68294564771763</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>2024</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>46</v>
+      </c>
+      <c r="D33">
+        <v>31</v>
+      </c>
+      <c r="E33">
+        <v>48</v>
+      </c>
+      <c r="F33">
+        <v>38</v>
+      </c>
+      <c r="G33">
+        <v>48</v>
+      </c>
+      <c r="H33">
+        <v>33</v>
+      </c>
+      <c r="I33">
+        <v>48</v>
+      </c>
+      <c r="J33">
+        <v>27</v>
+      </c>
+      <c r="K33">
+        <v>47</v>
+      </c>
+      <c r="L33">
+        <v>48</v>
+      </c>
+      <c r="M33">
+        <v>41</v>
+      </c>
+      <c r="N33">
+        <v>4</v>
+      </c>
+      <c r="O33">
+        <v>18</v>
+      </c>
+      <c r="P33">
+        <v>15</v>
+      </c>
+      <c r="Q33">
+        <v>61.56956069575283</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>2024</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>6</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34">
+        <v>17</v>
+      </c>
+      <c r="F34">
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <v>12</v>
+      </c>
+      <c r="H34">
+        <v>22</v>
+      </c>
+      <c r="I34">
+        <v>19</v>
+      </c>
+      <c r="J34">
+        <v>18</v>
+      </c>
+      <c r="K34">
+        <v>12</v>
+      </c>
+      <c r="L34">
+        <v>32</v>
+      </c>
+      <c r="M34">
+        <v>31</v>
+      </c>
+      <c r="N34">
+        <v>32</v>
+      </c>
+      <c r="O34">
+        <v>22</v>
+      </c>
+      <c r="P34">
+        <v>30</v>
+      </c>
+      <c r="Q34">
+        <v>25.61819488811676</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>2024</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
+        <v>33</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>27</v>
+      </c>
+      <c r="H35">
+        <v>10</v>
+      </c>
+      <c r="I35">
+        <v>2</v>
+      </c>
+      <c r="J35">
+        <v>21</v>
+      </c>
+      <c r="K35">
+        <v>19</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>42</v>
+      </c>
+      <c r="N35">
+        <v>14</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>11</v>
+      </c>
+      <c r="Q35">
+        <v>11.25650966017058</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>2024</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>11</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36">
+        <v>23</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="H36">
+        <v>20</v>
+      </c>
+      <c r="I36">
+        <v>25</v>
+      </c>
+      <c r="J36">
+        <v>15</v>
+      </c>
+      <c r="K36">
+        <v>36</v>
+      </c>
+      <c r="L36">
+        <v>20</v>
+      </c>
+      <c r="M36">
+        <v>17</v>
+      </c>
+      <c r="N36">
+        <v>9</v>
+      </c>
+      <c r="O36">
+        <v>15</v>
+      </c>
+      <c r="P36">
+        <v>26</v>
+      </c>
+      <c r="Q36">
+        <v>17.74855961053164</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>2024</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>43</v>
+      </c>
+      <c r="D37">
+        <v>40</v>
+      </c>
+      <c r="E37">
+        <v>47</v>
+      </c>
+      <c r="F37">
+        <v>43</v>
+      </c>
+      <c r="G37">
+        <v>40</v>
+      </c>
+      <c r="H37">
+        <v>34</v>
+      </c>
+      <c r="I37">
+        <v>37</v>
+      </c>
+      <c r="J37">
+        <v>44</v>
+      </c>
+      <c r="K37">
+        <v>29</v>
+      </c>
+      <c r="L37">
+        <v>15</v>
+      </c>
+      <c r="M37">
+        <v>35</v>
+      </c>
+      <c r="N37">
+        <v>21</v>
+      </c>
+      <c r="O37">
+        <v>37</v>
+      </c>
+      <c r="P37">
+        <v>44</v>
+      </c>
+      <c r="Q37">
+        <v>16.45453185535384</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>2024</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>28</v>
+      </c>
+      <c r="D38">
+        <v>28</v>
+      </c>
+      <c r="E38">
+        <v>39</v>
+      </c>
+      <c r="F38">
+        <v>40</v>
+      </c>
+      <c r="G38">
+        <v>38</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>18</v>
+      </c>
+      <c r="J38">
+        <v>13</v>
+      </c>
+      <c r="K38">
+        <v>27</v>
+      </c>
+      <c r="L38">
+        <v>33</v>
+      </c>
+      <c r="M38">
+        <v>15</v>
+      </c>
+      <c r="N38">
+        <v>45</v>
+      </c>
+      <c r="O38">
+        <v>34</v>
+      </c>
+      <c r="P38">
+        <v>38</v>
+      </c>
+      <c r="Q38">
+        <v>27.50312409078214</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>2024</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>35</v>
+      </c>
+      <c r="D39">
+        <v>10</v>
+      </c>
+      <c r="E39">
+        <v>24</v>
+      </c>
+      <c r="F39">
+        <v>21</v>
+      </c>
+      <c r="G39">
+        <v>37</v>
+      </c>
+      <c r="H39">
+        <v>39</v>
+      </c>
+      <c r="I39">
+        <v>43</v>
+      </c>
+      <c r="J39">
+        <v>33</v>
+      </c>
+      <c r="K39">
+        <v>39</v>
+      </c>
+      <c r="L39">
+        <v>42</v>
+      </c>
+      <c r="M39">
+        <v>45</v>
+      </c>
+      <c r="N39">
+        <v>6</v>
+      </c>
+      <c r="O39">
+        <v>30</v>
+      </c>
+      <c r="P39">
+        <v>35</v>
+      </c>
+      <c r="Q39">
+        <v>41.76408522041971</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>2024</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>38</v>
+      </c>
+      <c r="D40">
+        <v>27</v>
+      </c>
+      <c r="E40">
+        <v>16</v>
+      </c>
+      <c r="F40">
+        <v>13</v>
+      </c>
+      <c r="G40">
+        <v>6</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40">
+        <v>49</v>
+      </c>
+      <c r="K40">
+        <v>48</v>
+      </c>
+      <c r="L40">
+        <v>34</v>
+      </c>
+      <c r="M40">
+        <v>46</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40">
+        <v>4</v>
+      </c>
+      <c r="P40">
+        <v>4</v>
+      </c>
+      <c r="Q40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>2024</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>5</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>24</v>
+      </c>
+      <c r="I41">
+        <v>21</v>
+      </c>
+      <c r="J41">
+        <v>20</v>
+      </c>
+      <c r="K41">
+        <v>5</v>
+      </c>
+      <c r="L41">
+        <v>25</v>
+      </c>
+      <c r="M41">
+        <v>27</v>
+      </c>
+      <c r="N41">
+        <v>46</v>
+      </c>
+      <c r="O41">
+        <v>47</v>
+      </c>
+      <c r="P41">
+        <v>45</v>
+      </c>
+      <c r="Q41">
+        <v>22.42923089116594</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>2024</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>27</v>
+      </c>
+      <c r="D42">
+        <v>34</v>
+      </c>
+      <c r="E42">
+        <v>23</v>
+      </c>
+      <c r="F42">
+        <v>41</v>
+      </c>
+      <c r="G42">
+        <v>29</v>
+      </c>
+      <c r="H42">
+        <v>7</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <v>24</v>
+      </c>
+      <c r="K42">
+        <v>18</v>
+      </c>
+      <c r="L42">
+        <v>9</v>
+      </c>
+      <c r="M42">
+        <v>48</v>
+      </c>
+      <c r="N42">
+        <v>28</v>
+      </c>
+      <c r="O42">
+        <v>5</v>
+      </c>
+      <c r="P42">
+        <v>47</v>
+      </c>
+      <c r="Q42">
+        <v>13.41776542067314</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>2024</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>16</v>
+      </c>
+      <c r="D43">
+        <v>12</v>
+      </c>
+      <c r="E43">
+        <v>25</v>
+      </c>
+      <c r="F43">
+        <v>37</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+      <c r="H43">
+        <v>13</v>
+      </c>
+      <c r="I43">
+        <v>16</v>
+      </c>
+      <c r="J43">
+        <v>32</v>
+      </c>
+      <c r="K43">
+        <v>9</v>
+      </c>
+      <c r="L43">
+        <v>36</v>
+      </c>
+      <c r="M43">
+        <v>11</v>
+      </c>
+      <c r="N43">
+        <v>22</v>
+      </c>
+      <c r="O43">
+        <v>46</v>
+      </c>
+      <c r="P43">
+        <v>48</v>
+      </c>
+      <c r="Q43">
+        <v>32.63189943658134</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2024</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>30</v>
+      </c>
+      <c r="D44">
+        <v>41</v>
+      </c>
+      <c r="E44">
+        <v>26</v>
+      </c>
+      <c r="F44">
+        <v>32</v>
+      </c>
+      <c r="G44">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>19</v>
+      </c>
+      <c r="I44">
+        <v>32</v>
+      </c>
+      <c r="J44">
+        <v>16</v>
+      </c>
+      <c r="K44">
+        <v>37</v>
+      </c>
+      <c r="L44">
+        <v>41</v>
+      </c>
+      <c r="M44">
+        <v>3</v>
+      </c>
+      <c r="N44">
+        <v>38</v>
+      </c>
+      <c r="O44">
+        <v>33</v>
+      </c>
+      <c r="P44">
+        <v>41</v>
+      </c>
+      <c r="Q44">
+        <v>39.16517132457287</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2024</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45">
+        <v>43</v>
+      </c>
+      <c r="E45">
+        <v>30</v>
+      </c>
+      <c r="F45">
+        <v>14</v>
+      </c>
+      <c r="G45">
+        <v>34</v>
+      </c>
+      <c r="H45">
+        <v>9</v>
+      </c>
+      <c r="I45">
+        <v>17</v>
+      </c>
+      <c r="J45">
+        <v>7</v>
+      </c>
+      <c r="K45">
+        <v>6</v>
+      </c>
+      <c r="L45">
+        <v>19</v>
+      </c>
+      <c r="M45">
+        <v>8</v>
+      </c>
+      <c r="N45">
+        <v>33</v>
+      </c>
+      <c r="O45">
+        <v>7</v>
+      </c>
+      <c r="P45">
+        <v>3</v>
+      </c>
+      <c r="Q45">
+        <v>17.69515390934974</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2024</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>40</v>
+      </c>
+      <c r="D46">
+        <v>29</v>
+      </c>
+      <c r="E46">
+        <v>50</v>
+      </c>
+      <c r="F46">
+        <v>49</v>
+      </c>
+      <c r="G46">
+        <v>46</v>
+      </c>
+      <c r="H46">
+        <v>16</v>
+      </c>
+      <c r="I46">
+        <v>5</v>
+      </c>
+      <c r="J46">
+        <v>39</v>
+      </c>
+      <c r="K46">
+        <v>26</v>
+      </c>
+      <c r="L46">
+        <v>7</v>
+      </c>
+      <c r="M46">
+        <v>7</v>
+      </c>
+      <c r="N46">
+        <v>2</v>
+      </c>
+      <c r="O46">
+        <v>8</v>
+      </c>
+      <c r="P46">
+        <v>8</v>
+      </c>
+      <c r="Q46">
+        <v>12.88906173236351</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2024</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>8</v>
+      </c>
+      <c r="D47">
+        <v>2</v>
+      </c>
+      <c r="E47">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>14</v>
+      </c>
+      <c r="H47">
+        <v>21</v>
+      </c>
+      <c r="I47">
+        <v>30</v>
+      </c>
+      <c r="J47">
+        <v>17</v>
+      </c>
+      <c r="K47">
+        <v>16</v>
+      </c>
+      <c r="L47">
+        <v>39</v>
+      </c>
+      <c r="M47">
+        <v>10</v>
+      </c>
+      <c r="N47">
+        <v>34</v>
+      </c>
+      <c r="O47">
+        <v>12</v>
+      </c>
+      <c r="P47">
+        <v>25</v>
+      </c>
+      <c r="Q47">
+        <v>33.13182498916174</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2024</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>49</v>
+      </c>
+      <c r="D48">
+        <v>50</v>
+      </c>
+      <c r="E48">
+        <v>45</v>
+      </c>
+      <c r="F48">
+        <v>50</v>
+      </c>
+      <c r="G48">
+        <v>50</v>
+      </c>
+      <c r="H48">
+        <v>46</v>
+      </c>
+      <c r="I48">
+        <v>31</v>
+      </c>
+      <c r="J48">
+        <v>30</v>
+      </c>
+      <c r="K48">
+        <v>45</v>
+      </c>
+      <c r="L48">
+        <v>38</v>
+      </c>
+      <c r="M48">
+        <v>23</v>
+      </c>
+      <c r="N48">
+        <v>27</v>
+      </c>
+      <c r="O48">
+        <v>29</v>
+      </c>
+      <c r="P48">
+        <v>31</v>
+      </c>
+      <c r="Q48">
+        <v>33.05209334741966</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2024</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>32</v>
+      </c>
+      <c r="D49">
+        <v>9</v>
+      </c>
+      <c r="E49">
+        <v>15</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>11</v>
+      </c>
+      <c r="H49">
+        <v>37</v>
+      </c>
+      <c r="I49">
+        <v>29</v>
+      </c>
+      <c r="J49">
+        <v>43</v>
+      </c>
+      <c r="K49">
+        <v>14</v>
+      </c>
+      <c r="L49">
+        <v>6</v>
+      </c>
+      <c r="M49">
+        <v>49</v>
+      </c>
+      <c r="N49">
+        <v>10</v>
+      </c>
+      <c r="O49">
+        <v>44</v>
+      </c>
+      <c r="P49">
+        <v>49</v>
+      </c>
+      <c r="Q49">
+        <v>12.52867894350944</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2024</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>33</v>
+      </c>
+      <c r="D50">
+        <v>22</v>
+      </c>
+      <c r="E50">
+        <v>12</v>
+      </c>
+      <c r="F50">
+        <v>28</v>
+      </c>
+      <c r="G50">
+        <v>47</v>
+      </c>
+      <c r="H50">
+        <v>29</v>
+      </c>
+      <c r="I50">
+        <v>26</v>
+      </c>
+      <c r="J50">
+        <v>38</v>
+      </c>
+      <c r="K50">
+        <v>44</v>
+      </c>
+      <c r="L50">
+        <v>21</v>
+      </c>
+      <c r="M50">
+        <v>29</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>9</v>
+      </c>
+      <c r="P50">
+        <v>13</v>
+      </c>
+      <c r="Q50">
+        <v>18.64600059800251</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2024</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>21</v>
+      </c>
+      <c r="E51">
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <v>17</v>
+      </c>
+      <c r="G51">
+        <v>16</v>
+      </c>
+      <c r="H51">
+        <v>25</v>
+      </c>
+      <c r="I51">
+        <v>46</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51">
+        <v>20</v>
+      </c>
+      <c r="L51">
+        <v>5</v>
+      </c>
+      <c r="M51">
+        <v>28</v>
+      </c>
+      <c r="N51">
+        <v>19</v>
+      </c>
+      <c r="O51">
+        <v>35</v>
+      </c>
+      <c r="P51">
+        <v>17</v>
+      </c>
+      <c r="Q51">
+        <v>11.94906506228042</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
